--- a/dataset_new proposals.xlsx
+++ b/dataset_new proposals.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avyr_\Desktop\Paper Metaheuristic Review 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA3E8FE5-0460-4F85-AE4E-F8FAFEDD6A2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11C82C7F-16A9-4744-BAB9-ED8373057628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="new approaches only" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4298" uniqueCount="1967">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4298" uniqueCount="1965">
   <si>
     <t>Authors</t>
   </si>
@@ -3906,9 +3906,6 @@
   </si>
   <si>
     <t>Predator evasión, Lévy Flight, Gaussian mutation, and population consolidation</t>
-  </si>
-  <si>
-    <t>CEC2014; CEC2017; CEC2020; CEC2019</t>
   </si>
   <si>
     <t>The Rabbit and Turtle Algorithm</t>
@@ -5426,9 +5423,6 @@
     <t>Dark Forest Algorithm</t>
   </si>
   <si>
-    <t>DEA</t>
-  </si>
-  <si>
     <t>The superiority among civilizations and the universe's dark forest law</t>
   </si>
   <si>
@@ -5651,9 +5645,6 @@
     <t>Smart Antennas with Anti-Jamming; Narrowband Microstrip Patch Antenna Design</t>
   </si>
   <si>
-    <t>PSO; SSA</t>
-  </si>
-  <si>
     <t>Feature Selection</t>
   </si>
   <si>
@@ -5988,6 +5979,9 @@
   </si>
   <si>
     <t>Friedman Test; Kruskal-Wallis Test; Holm Procedure</t>
+  </si>
+  <si>
+    <t>DFA</t>
   </si>
 </sst>
 </file>
@@ -6593,42 +6587,42 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8838D940-E37E-4DA2-A86C-5A25AA49C281}">
   <dimension ref="A1:AK135"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.33203125" customWidth="1"/>
-    <col min="3" max="3" width="55.88671875" customWidth="1"/>
-    <col min="4" max="4" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.21875" customWidth="1"/>
-    <col min="8" max="10" width="11.5546875" customWidth="1"/>
-    <col min="11" max="11" width="54.5546875" customWidth="1"/>
+    <col min="1" max="1" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.28515625" customWidth="1"/>
+    <col min="3" max="3" width="55.85546875" customWidth="1"/>
+    <col min="4" max="4" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" customWidth="1"/>
+    <col min="8" max="10" width="11.5703125" customWidth="1"/>
+    <col min="11" max="11" width="54.5703125" customWidth="1"/>
     <col min="12" max="12" width="14" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="15.77734375" customWidth="1"/>
-    <col min="15" max="15" width="13.33203125" customWidth="1"/>
-    <col min="16" max="16" width="11.5546875" customWidth="1"/>
-    <col min="17" max="17" width="15.88671875" style="47" customWidth="1"/>
+    <col min="14" max="14" width="15.7109375" customWidth="1"/>
+    <col min="15" max="15" width="13.28515625" customWidth="1"/>
+    <col min="16" max="16" width="11.5703125" customWidth="1"/>
+    <col min="17" max="17" width="15.85546875" style="47" customWidth="1"/>
     <col min="18" max="18" width="19" customWidth="1"/>
-    <col min="19" max="19" width="50.88671875" customWidth="1"/>
-    <col min="20" max="20" width="16.77734375" customWidth="1"/>
-    <col min="21" max="21" width="17.6640625" customWidth="1"/>
-    <col min="22" max="22" width="17.5546875" customWidth="1"/>
-    <col min="23" max="23" width="21.33203125" customWidth="1"/>
-    <col min="24" max="24" width="19.44140625" customWidth="1"/>
-    <col min="25" max="25" width="22.5546875" customWidth="1"/>
-    <col min="26" max="26" width="28.33203125" customWidth="1"/>
-    <col min="27" max="27" width="47.5546875" customWidth="1"/>
-    <col min="28" max="28" width="13.21875" customWidth="1"/>
-    <col min="29" max="29" width="159.77734375" customWidth="1"/>
-    <col min="30" max="30" width="19.109375" customWidth="1"/>
-    <col min="31" max="31" width="108.21875" customWidth="1"/>
-    <col min="32" max="32" width="20.88671875" customWidth="1"/>
-    <col min="33" max="33" width="72.44140625" customWidth="1"/>
-    <col min="36" max="36" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="50.85546875" customWidth="1"/>
+    <col min="20" max="20" width="16.7109375" customWidth="1"/>
+    <col min="21" max="21" width="17.7109375" customWidth="1"/>
+    <col min="22" max="22" width="17.5703125" customWidth="1"/>
+    <col min="23" max="23" width="21.28515625" customWidth="1"/>
+    <col min="24" max="24" width="19.42578125" customWidth="1"/>
+    <col min="25" max="25" width="22.5703125" customWidth="1"/>
+    <col min="26" max="26" width="28.28515625" customWidth="1"/>
+    <col min="27" max="27" width="47.5703125" customWidth="1"/>
+    <col min="28" max="28" width="13.28515625" customWidth="1"/>
+    <col min="29" max="29" width="159.7109375" customWidth="1"/>
+    <col min="30" max="30" width="19.140625" customWidth="1"/>
+    <col min="31" max="31" width="108.28515625" customWidth="1"/>
+    <col min="32" max="32" width="20.85546875" customWidth="1"/>
+    <col min="33" max="33" width="72.42578125" customWidth="1"/>
+    <col min="36" max="36" width="21.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:37" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6636,7 +6630,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1852</v>
+        <v>1850</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
@@ -6657,7 +6651,7 @@
         <v>7</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>1828</v>
+        <v>1826</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>8</v>
@@ -6717,7 +6711,7 @@
         <v>15</v>
       </c>
       <c r="AE1" s="27" t="s">
-        <v>1875</v>
+        <v>1872</v>
       </c>
       <c r="AF1" s="28" t="s">
         <v>13</v>
@@ -6732,11 +6726,11 @@
         <v>5</v>
       </c>
       <c r="AJ1" s="29" t="s">
-        <v>1885</v>
+        <v>1882</v>
       </c>
       <c r="AK1" s="29"/>
     </row>
-    <row r="2" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -6804,25 +6798,25 @@
         <v>1006</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="AD2" s="2" t="s">
         <v>1047</v>
       </c>
       <c r="AE2" s="8" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH2" s="2" t="s">
         <v>26</v>
@@ -6834,7 +6828,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -6902,13 +6896,13 @@
         <v>1006</v>
       </c>
       <c r="AA3" s="2" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AB3" s="8" t="s">
         <v>35</v>
       </c>
       <c r="AC3" s="2" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="AD3" s="2" t="s">
         <v>1048</v>
@@ -6917,10 +6911,10 @@
         <v>996</v>
       </c>
       <c r="AF3" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG3" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH3" s="2" t="s">
         <v>26</v>
@@ -6932,7 +6926,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -7003,25 +6997,25 @@
         <v>26</v>
       </c>
       <c r="AA4" s="2" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="AB4" s="2" t="s">
         <v>77</v>
       </c>
       <c r="AC4" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD4" s="2" t="s">
         <v>1049</v>
       </c>
       <c r="AE4" s="8" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="AF4" s="8" t="s">
         <v>237</v>
       </c>
       <c r="AG4" s="8" t="s">
-        <v>1877</v>
+        <v>1874</v>
       </c>
       <c r="AH4" s="2" t="s">
         <v>26</v>
@@ -7033,7 +7027,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -7092,22 +7086,22 @@
         <v>1013</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="AB5" s="2" t="s">
         <v>54</v>
       </c>
       <c r="AC5" s="2" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AD5" s="2" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AE5" s="8" t="s">
         <v>997</v>
@@ -7116,19 +7110,19 @@
         <v>25</v>
       </c>
       <c r="AG5" s="8" t="s">
-        <v>1949</v>
+        <v>1946</v>
       </c>
       <c r="AH5" s="2" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AI5" s="2" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AJ5" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -7199,25 +7193,25 @@
         <v>1006</v>
       </c>
       <c r="AA6" s="2" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="AB6" s="8" t="s">
         <v>62</v>
       </c>
       <c r="AC6" s="2" t="s">
-        <v>1830</v>
+        <v>1828</v>
       </c>
       <c r="AD6" s="30" t="s">
         <v>1012</v>
       </c>
       <c r="AE6" s="8" t="s">
-        <v>1963</v>
+        <v>1960</v>
       </c>
       <c r="AF6" s="8" t="s">
-        <v>1946</v>
+        <v>1943</v>
       </c>
       <c r="AG6" s="8" t="s">
-        <v>1884</v>
+        <v>1881</v>
       </c>
       <c r="AH6" s="2" t="s">
         <v>1216</v>
@@ -7229,7 +7223,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="7" spans="1:37" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:37" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -7264,7 +7258,7 @@
         <v>70</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="M7" s="4" t="s">
         <v>993</v>
@@ -7297,13 +7291,13 @@
         <v>1034</v>
       </c>
       <c r="AA7" s="4" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="AB7" s="4" t="s">
         <v>77</v>
       </c>
       <c r="AC7" s="31" t="s">
-        <v>1886</v>
+        <v>1883</v>
       </c>
       <c r="AD7" s="4" t="s">
         <v>1030</v>
@@ -7312,10 +7306,10 @@
         <v>997</v>
       </c>
       <c r="AF7" s="4" t="s">
-        <v>1887</v>
+        <v>1884</v>
       </c>
       <c r="AG7" s="4" t="s">
-        <v>1954</v>
+        <v>1951</v>
       </c>
       <c r="AH7" s="4" t="s">
         <v>26</v>
@@ -7327,7 +7321,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:37" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:37" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -7392,13 +7386,13 @@
         <v>1006</v>
       </c>
       <c r="AA8" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="AB8" s="4" t="s">
         <v>77</v>
       </c>
       <c r="AC8" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD8" s="4" t="s">
         <v>1031</v>
@@ -7407,10 +7401,10 @@
         <v>1028</v>
       </c>
       <c r="AF8" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG8" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH8" s="4" t="s">
         <v>26</v>
@@ -7422,7 +7416,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:37" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:37" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -7487,13 +7481,13 @@
         <v>26</v>
       </c>
       <c r="AA9" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="AB9" s="4" t="s">
         <v>84</v>
       </c>
       <c r="AC9" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD9" s="4" t="s">
         <v>1032</v>
@@ -7502,10 +7496,10 @@
         <v>1028</v>
       </c>
       <c r="AF9" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG9" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH9" s="4" t="s">
         <v>26</v>
@@ -7517,7 +7511,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:37" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:37" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -7555,7 +7549,7 @@
         <v>1011</v>
       </c>
       <c r="N10" s="11" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="O10" s="4" t="s">
         <v>1017</v>
@@ -7582,25 +7576,25 @@
         <v>1006</v>
       </c>
       <c r="AA10" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="AB10" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC10" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD10" s="4" t="s">
         <v>1042</v>
       </c>
       <c r="AE10" s="4" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="AF10" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG10" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH10" s="4" t="s">
         <v>26</v>
@@ -7612,7 +7606,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="11" spans="1:37" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:37" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -7674,28 +7668,28 @@
         <v>992</v>
       </c>
       <c r="V11" s="4" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AA11" s="4" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AB11" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC11" s="4" t="s">
-        <v>1914</v>
+        <v>1911</v>
       </c>
       <c r="AD11" s="4" t="s">
-        <v>1851</v>
+        <v>1849</v>
       </c>
       <c r="AE11" s="4" t="s">
         <v>1028</v>
       </c>
       <c r="AF11" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG11" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH11" s="4" t="s">
         <v>26</v>
@@ -7707,7 +7701,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -7742,7 +7736,7 @@
         <v>109</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="M12" s="13" t="s">
         <v>993</v>
@@ -7775,13 +7769,13 @@
         <v>1085</v>
       </c>
       <c r="AA12" s="2" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="AB12" s="13" t="s">
         <v>1086</v>
       </c>
       <c r="AC12" s="2" t="s">
-        <v>1930</v>
+        <v>1927</v>
       </c>
       <c r="AD12" s="32" t="s">
         <v>1076</v>
@@ -7793,7 +7787,7 @@
         <v>25</v>
       </c>
       <c r="AG12" s="13" t="s">
-        <v>1949</v>
+        <v>1946</v>
       </c>
       <c r="AH12" s="7" t="s">
         <v>1216</v>
@@ -7805,7 +7799,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="13" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -7843,7 +7837,7 @@
         <v>1011</v>
       </c>
       <c r="N13" s="16" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>1088</v>
@@ -7870,13 +7864,13 @@
         <v>1098</v>
       </c>
       <c r="AA13" s="2" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AB13" s="13" t="s">
         <v>62</v>
       </c>
       <c r="AC13" s="13" t="s">
-        <v>1929</v>
+        <v>1926</v>
       </c>
       <c r="AD13" s="13" t="s">
         <v>1077</v>
@@ -7885,10 +7879,10 @@
         <v>1081</v>
       </c>
       <c r="AF13" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG13" s="13" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH13" s="13" t="s">
         <v>26</v>
@@ -7900,7 +7894,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="14" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -7941,7 +7935,7 @@
         <v>1011</v>
       </c>
       <c r="N14" s="16" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>1099</v>
@@ -7968,25 +7962,25 @@
         <v>1102</v>
       </c>
       <c r="AA14" s="2" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="AB14" s="13" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC14" s="2" t="s">
-        <v>1901</v>
+        <v>1898</v>
       </c>
       <c r="AD14" s="13" t="s">
         <v>1078</v>
       </c>
       <c r="AE14" s="13" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="AF14" s="2" t="s">
-        <v>1947</v>
+        <v>1944</v>
       </c>
       <c r="AG14" s="13" t="s">
-        <v>1951</v>
+        <v>1948</v>
       </c>
       <c r="AH14" s="13" t="s">
         <v>1064</v>
@@ -7998,7 +7992,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -8036,7 +8030,7 @@
         <v>1011</v>
       </c>
       <c r="N15" s="16" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>1089</v>
@@ -8063,13 +8057,13 @@
         <v>1006</v>
       </c>
       <c r="AA15" s="2" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="AB15" s="13" t="s">
         <v>1126</v>
       </c>
       <c r="AC15" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD15" s="13" t="s">
         <v>1079</v>
@@ -8078,10 +8072,10 @@
         <v>1028</v>
       </c>
       <c r="AF15" s="13" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG15" s="13" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH15" s="13" t="s">
         <v>26</v>
@@ -8093,7 +8087,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -8158,13 +8152,13 @@
         <v>1108</v>
       </c>
       <c r="AA16" s="2" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AB16" s="13" t="s">
         <v>1281</v>
       </c>
       <c r="AC16" s="2" t="s">
-        <v>1831</v>
+        <v>1829</v>
       </c>
       <c r="AD16" s="32" t="s">
         <v>1080</v>
@@ -8173,10 +8167,10 @@
         <v>1028</v>
       </c>
       <c r="AF16" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG16" s="13" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH16" s="13" t="s">
         <v>26</v>
@@ -8188,7 +8182,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -8226,13 +8220,13 @@
         <v>993</v>
       </c>
       <c r="N17" s="11" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="O17" s="11" t="s">
         <v>1109</v>
       </c>
       <c r="P17" s="11" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="Q17" s="11" t="s">
         <v>1117</v>
@@ -8241,47 +8235,47 @@
         <v>24</v>
       </c>
       <c r="S17" s="11" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="T17" s="11" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="V17" s="4" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="Z17" s="11"/>
       <c r="AA17" s="11" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AB17" s="11" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AC17" s="11" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AD17" s="11" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AE17" s="11" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AF17" s="11" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AG17" s="11" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AH17" s="11" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AI17" s="11" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AJ17" s="11" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
     </row>
-    <row r="18" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -8322,7 +8316,7 @@
         <v>1011</v>
       </c>
       <c r="N18" s="11" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="O18" s="11" t="s">
         <v>1110</v>
@@ -8349,13 +8343,13 @@
         <v>1123</v>
       </c>
       <c r="AA18" s="4" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="AB18" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC18" s="11" t="s">
-        <v>1888</v>
+        <v>1885</v>
       </c>
       <c r="AD18" s="11" t="s">
         <v>1128</v>
@@ -8364,10 +8358,10 @@
         <v>1132</v>
       </c>
       <c r="AF18" s="11" t="s">
-        <v>1941</v>
+        <v>1938</v>
       </c>
       <c r="AG18" s="11" t="s">
-        <v>1863</v>
+        <v>1860</v>
       </c>
       <c r="AH18" s="11" t="s">
         <v>1064</v>
@@ -8379,7 +8373,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="19" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -8444,10 +8438,10 @@
         <v>26</v>
       </c>
       <c r="AA19" s="4" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AB19" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC19" s="11" t="s">
         <v>1127</v>
@@ -8459,10 +8453,10 @@
         <v>1081</v>
       </c>
       <c r="AF19" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG19" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH19" s="12" t="s">
         <v>1216</v>
@@ -8474,7 +8468,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="20" spans="1:36" s="4" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:36" s="4" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -8539,25 +8533,25 @@
         <v>1124</v>
       </c>
       <c r="AA20" s="4" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="AB20" s="11" t="s">
         <v>1126</v>
       </c>
       <c r="AC20" s="48" t="s">
-        <v>1932</v>
+        <v>1929</v>
       </c>
       <c r="AD20" s="11" t="s">
         <v>1130</v>
       </c>
       <c r="AE20" s="11" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="AF20" s="11" t="s">
-        <v>1942</v>
+        <v>1939</v>
       </c>
       <c r="AG20" s="11" t="s">
-        <v>1889</v>
+        <v>1886</v>
       </c>
       <c r="AH20" s="11" t="s">
         <v>26</v>
@@ -8569,7 +8563,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -8607,7 +8601,7 @@
         <v>1011</v>
       </c>
       <c r="N21" s="11" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="O21" s="11" t="s">
         <v>1113</v>
@@ -8634,25 +8628,25 @@
         <v>1125</v>
       </c>
       <c r="AA21" s="4" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AB21" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC21" s="11" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="AD21" s="11" t="s">
         <v>1131</v>
       </c>
       <c r="AE21" s="11" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="AF21" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG21" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH21" s="11" t="s">
         <v>26</v>
@@ -8664,7 +8658,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -8736,13 +8730,13 @@
         <v>1140</v>
       </c>
       <c r="AA22" s="2" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="AB22" s="13" t="s">
         <v>1141</v>
       </c>
       <c r="AC22" s="13" t="s">
-        <v>1890</v>
+        <v>1887</v>
       </c>
       <c r="AD22" s="13" t="s">
         <v>1142</v>
@@ -8751,22 +8745,22 @@
         <v>996</v>
       </c>
       <c r="AF22" s="13" t="s">
-        <v>1945</v>
+        <v>1942</v>
       </c>
       <c r="AG22" s="13" t="s">
-        <v>1909</v>
+        <v>1906</v>
       </c>
       <c r="AH22" s="13" t="s">
         <v>1216</v>
       </c>
       <c r="AI22" s="14" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="AJ22" s="13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -8801,7 +8795,7 @@
         <v>109</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="M23" s="13" t="s">
         <v>993</v>
@@ -8838,13 +8832,13 @@
         <v>1147</v>
       </c>
       <c r="AA23" s="2" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AB23" s="13" t="s">
         <v>1148</v>
       </c>
       <c r="AC23" s="13" t="s">
-        <v>1917</v>
+        <v>1914</v>
       </c>
       <c r="AD23" s="13" t="s">
         <v>1149</v>
@@ -8853,10 +8847,10 @@
         <v>1028</v>
       </c>
       <c r="AF23" s="13" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG23" s="13" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH23" s="15" t="s">
         <v>1216</v>
@@ -8868,7 +8862,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="24" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -8937,13 +8931,13 @@
         <v>1133</v>
       </c>
       <c r="AA24" s="2" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AB24" s="13" t="s">
         <v>77</v>
       </c>
       <c r="AC24" s="13" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="AD24" s="13" t="s">
         <v>1154</v>
@@ -8952,10 +8946,10 @@
         <v>1081</v>
       </c>
       <c r="AF24" s="13" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG24" s="13" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH24" s="13" t="s">
         <v>26</v>
@@ -8967,7 +8961,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -9036,25 +9030,25 @@
         <v>1133</v>
       </c>
       <c r="AA25" s="2" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AB25" s="13" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC25" s="13" t="s">
-        <v>1832</v>
+        <v>1830</v>
       </c>
       <c r="AD25" s="13" t="s">
         <v>1158</v>
       </c>
       <c r="AE25" s="13" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="AF25" s="13" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG25" s="13" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH25" s="13" t="s">
         <v>26</v>
@@ -9066,7 +9060,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -9143,25 +9137,25 @@
         <v>1163</v>
       </c>
       <c r="AA26" s="11" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="AB26" s="11" t="s">
         <v>77</v>
       </c>
       <c r="AC26" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD26" s="11" t="s">
         <v>1164</v>
       </c>
       <c r="AE26" s="11" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="AF26" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG26" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH26" s="11" t="s">
         <v>26</v>
@@ -9173,7 +9167,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="27" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -9250,25 +9244,25 @@
         <v>1170</v>
       </c>
       <c r="AA27" s="11" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="AB27" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC27" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD27" s="11" t="s">
         <v>1171</v>
       </c>
       <c r="AE27" s="11" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="AF27" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG27" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH27" s="11" t="s">
         <v>26</v>
@@ -9280,7 +9274,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -9357,13 +9351,13 @@
         <v>1170</v>
       </c>
       <c r="AA28" s="11" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="AB28" s="11" t="s">
         <v>1126</v>
       </c>
       <c r="AC28" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD28" s="11" t="s">
         <v>1177</v>
@@ -9372,10 +9366,10 @@
         <v>1028</v>
       </c>
       <c r="AF28" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG28" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH28" s="11" t="s">
         <v>26</v>
@@ -9387,7 +9381,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -9467,13 +9461,13 @@
         <v>1133</v>
       </c>
       <c r="AA29" s="4" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AB29" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC29" s="11" t="s">
-        <v>1920</v>
+        <v>1917</v>
       </c>
       <c r="AD29" s="11" t="s">
         <v>1182</v>
@@ -9482,10 +9476,10 @@
         <v>1183</v>
       </c>
       <c r="AF29" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG29" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH29" s="12" t="s">
         <v>1216</v>
@@ -9497,7 +9491,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="30" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -9532,7 +9526,7 @@
         <v>236</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="M30" s="11" t="s">
         <v>993</v>
@@ -9577,13 +9571,13 @@
         <v>1190</v>
       </c>
       <c r="AA30" s="11" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="AB30" s="11" t="s">
         <v>77</v>
       </c>
       <c r="AC30" s="11" t="s">
-        <v>1892</v>
+        <v>1889</v>
       </c>
       <c r="AD30" s="11" t="s">
         <v>1191</v>
@@ -9595,7 +9589,7 @@
         <v>237</v>
       </c>
       <c r="AG30" s="11" t="s">
-        <v>1855</v>
+        <v>1852</v>
       </c>
       <c r="AH30" s="12" t="s">
         <v>1216</v>
@@ -9607,7 +9601,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="31" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -9642,7 +9636,7 @@
         <v>109</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>993</v>
@@ -9687,13 +9681,13 @@
         <v>1266</v>
       </c>
       <c r="AA31" s="2" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AB31" s="16" t="s">
         <v>1267</v>
       </c>
       <c r="AC31" s="16" t="s">
-        <v>1842</v>
+        <v>1840</v>
       </c>
       <c r="AD31" s="16" t="s">
         <v>1268</v>
@@ -9702,10 +9696,10 @@
         <v>1081</v>
       </c>
       <c r="AF31" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG31" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH31" s="17" t="s">
         <v>1216</v>
@@ -9717,7 +9711,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="32" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -9797,13 +9791,13 @@
         <v>1275</v>
       </c>
       <c r="AA32" s="2" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AB32" s="16" t="s">
         <v>54</v>
       </c>
       <c r="AC32" s="16" t="s">
-        <v>1833</v>
+        <v>1831</v>
       </c>
       <c r="AD32" s="16" t="s">
         <v>1276</v>
@@ -9812,10 +9806,10 @@
         <v>1081</v>
       </c>
       <c r="AF32" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG32" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH32" s="16" t="s">
         <v>26</v>
@@ -9827,7 +9821,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="33" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -9889,7 +9883,7 @@
         <v>1146</v>
       </c>
       <c r="V33" s="16" t="s">
-        <v>1829</v>
+        <v>1827</v>
       </c>
       <c r="W33" s="16" t="s">
         <v>1279</v>
@@ -9904,25 +9898,25 @@
         <v>1133</v>
       </c>
       <c r="AA33" s="16" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="AB33" s="16" t="s">
         <v>1281</v>
       </c>
       <c r="AC33" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD33" s="16" t="s">
         <v>1282</v>
       </c>
       <c r="AE33" s="16" t="s">
-        <v>1964</v>
+        <v>1961</v>
       </c>
       <c r="AF33" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG33" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH33" s="16" t="s">
         <v>26</v>
@@ -9934,7 +9928,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="34" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -9969,7 +9963,7 @@
         <v>268</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="M34" s="13" t="s">
         <v>993</v>
@@ -9997,32 +9991,32 @@
       </c>
       <c r="U34" s="16"/>
       <c r="V34" s="16" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="W34" s="16"/>
       <c r="X34" s="16"/>
       <c r="Y34" s="16"/>
       <c r="Z34" s="16"/>
       <c r="AA34" s="2" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AB34" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC34" s="16" t="s">
-        <v>1927</v>
+        <v>1924</v>
       </c>
       <c r="AD34" s="16" t="s">
-        <v>1845</v>
+        <v>1843</v>
       </c>
       <c r="AE34" s="16" t="s">
         <v>1028</v>
       </c>
       <c r="AF34" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG34" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH34" s="16" t="s">
         <v>26</v>
@@ -10034,7 +10028,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -10090,16 +10084,16 @@
         <v>24</v>
       </c>
       <c r="S35" s="16" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="T35" s="16" t="s">
         <v>1122</v>
       </c>
       <c r="U35" s="16" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="V35" s="16" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="W35" s="16" t="s">
         <v>1288</v>
@@ -10110,37 +10104,37 @@
       <c r="Y35" s="16"/>
       <c r="Z35" s="16"/>
       <c r="AA35" s="2" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="AB35" s="16" t="s">
-        <v>1290</v>
+        <v>1254</v>
       </c>
       <c r="AC35" s="16" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AD35" s="16" t="s">
-        <v>1854</v>
+        <v>1820</v>
       </c>
       <c r="AE35" s="16" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AF35" s="16" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AG35" s="16" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AH35" s="16" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AI35" s="16" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AJ35" s="16" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
     </row>
-    <row r="36" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -10181,16 +10175,16 @@
         <v>1011</v>
       </c>
       <c r="N36" s="11" t="s">
+        <v>1294</v>
+      </c>
+      <c r="O36" s="11" t="s">
         <v>1295</v>
       </c>
-      <c r="O36" s="11" t="s">
+      <c r="P36" s="11" t="s">
         <v>1296</v>
       </c>
-      <c r="P36" s="11" t="s">
+      <c r="Q36" s="43" t="s">
         <v>1297</v>
-      </c>
-      <c r="Q36" s="43" t="s">
-        <v>1298</v>
       </c>
       <c r="R36" s="11" t="s">
         <v>24</v>
@@ -10208,37 +10202,37 @@
         <v>1008</v>
       </c>
       <c r="W36" s="11" t="s">
+        <v>1298</v>
+      </c>
+      <c r="X36" s="11" t="s">
         <v>1299</v>
-      </c>
-      <c r="X36" s="11" t="s">
-        <v>1300</v>
       </c>
       <c r="Y36" s="11" t="s">
         <v>1133</v>
       </c>
       <c r="Z36" s="11" t="s">
+        <v>1300</v>
+      </c>
+      <c r="AA36" s="4" t="s">
+        <v>1845</v>
+      </c>
+      <c r="AB36" s="11" t="s">
         <v>1301</v>
       </c>
-      <c r="AA36" s="4" t="s">
-        <v>1847</v>
-      </c>
-      <c r="AB36" s="11" t="s">
+      <c r="AC36" s="11" t="s">
+        <v>1899</v>
+      </c>
+      <c r="AD36" s="11" t="s">
         <v>1302</v>
-      </c>
-      <c r="AC36" s="11" t="s">
-        <v>1902</v>
-      </c>
-      <c r="AD36" s="11" t="s">
-        <v>1303</v>
       </c>
       <c r="AE36" s="11" t="s">
         <v>1081</v>
       </c>
       <c r="AF36" s="11" t="s">
-        <v>1943</v>
+        <v>1940</v>
       </c>
       <c r="AG36" s="11" t="s">
-        <v>1952</v>
+        <v>1949</v>
       </c>
       <c r="AH36" s="11" t="s">
         <v>26</v>
@@ -10250,7 +10244,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="37" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -10294,19 +10288,19 @@
         <v>1054</v>
       </c>
       <c r="O37" s="11" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="P37" s="11" t="s">
         <v>1242</v>
       </c>
       <c r="Q37" s="11" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="R37" s="11" t="s">
         <v>24</v>
       </c>
       <c r="S37" s="11" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="T37" s="11" t="s">
         <v>1122</v>
@@ -10316,33 +10310,33 @@
         <v>1008</v>
       </c>
       <c r="W37" s="11" t="s">
+        <v>1305</v>
+      </c>
+      <c r="X37" s="11" t="s">
         <v>1306</v>
-      </c>
-      <c r="X37" s="11" t="s">
-        <v>1307</v>
       </c>
       <c r="Y37" s="11"/>
       <c r="Z37" s="11"/>
       <c r="AA37" s="4" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AB37" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC37" s="43" t="s">
-        <v>1866</v>
+        <v>1863</v>
       </c>
       <c r="AD37" s="11" t="s">
-        <v>1867</v>
+        <v>1864</v>
       </c>
       <c r="AE37" s="11" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="AF37" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG37" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH37" s="11" t="s">
         <v>26</v>
@@ -10354,7 +10348,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="38" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -10398,13 +10392,13 @@
         <v>994</v>
       </c>
       <c r="O38" s="11" t="s">
+        <v>1307</v>
+      </c>
+      <c r="P38" s="11" t="s">
         <v>1308</v>
       </c>
-      <c r="P38" s="11" t="s">
+      <c r="Q38" s="43" t="s">
         <v>1309</v>
-      </c>
-      <c r="Q38" s="43" t="s">
-        <v>1310</v>
       </c>
       <c r="R38" s="11" t="s">
         <v>24</v>
@@ -10422,37 +10416,37 @@
         <v>1008</v>
       </c>
       <c r="W38" s="11" t="s">
+        <v>1310</v>
+      </c>
+      <c r="X38" s="11" t="s">
         <v>1311</v>
-      </c>
-      <c r="X38" s="11" t="s">
-        <v>1312</v>
       </c>
       <c r="Y38" s="11" t="s">
         <v>1133</v>
       </c>
       <c r="Z38" s="11" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="AA38" s="11" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="AB38" s="11" t="s">
         <v>54</v>
       </c>
       <c r="AC38" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD38" s="11" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="AE38" s="11" t="s">
         <v>1081</v>
       </c>
       <c r="AF38" s="11" t="s">
-        <v>1943</v>
+        <v>1940</v>
       </c>
       <c r="AG38" s="11" t="s">
-        <v>1953</v>
+        <v>1950</v>
       </c>
       <c r="AH38" s="11" t="s">
         <v>26</v>
@@ -10464,7 +10458,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="39" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -10502,13 +10496,13 @@
         <v>994</v>
       </c>
       <c r="O39" s="11" t="s">
+        <v>1313</v>
+      </c>
+      <c r="P39" s="11" t="s">
         <v>1314</v>
       </c>
-      <c r="P39" s="11" t="s">
+      <c r="Q39" s="43" t="s">
         <v>1315</v>
-      </c>
-      <c r="Q39" s="43" t="s">
-        <v>1316</v>
       </c>
       <c r="R39" s="11" t="s">
         <v>24</v>
@@ -10526,37 +10520,37 @@
         <v>1008</v>
       </c>
       <c r="W39" s="11" t="s">
+        <v>1316</v>
+      </c>
+      <c r="X39" s="11" t="s">
         <v>1317</v>
       </c>
-      <c r="X39" s="11" t="s">
+      <c r="Y39" s="11" t="s">
         <v>1318</v>
       </c>
-      <c r="Y39" s="11" t="s">
+      <c r="Z39" s="11" t="s">
         <v>1319</v>
       </c>
-      <c r="Z39" s="11" t="s">
-        <v>1320</v>
-      </c>
       <c r="AA39" s="4" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AB39" s="11" t="s">
         <v>62</v>
       </c>
       <c r="AC39" s="11" t="s">
-        <v>1913</v>
+        <v>1910</v>
       </c>
       <c r="AD39" s="11" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="AE39" s="11" t="s">
-        <v>1959</v>
+        <v>1956</v>
       </c>
       <c r="AF39" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG39" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH39" s="11" t="s">
         <v>26</v>
@@ -10568,7 +10562,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -10606,16 +10600,16 @@
         <v>993</v>
       </c>
       <c r="N40" s="11" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="O40" s="11" t="s">
+        <v>1321</v>
+      </c>
+      <c r="P40" s="11" t="s">
         <v>1322</v>
       </c>
-      <c r="P40" s="11" t="s">
+      <c r="Q40" s="11" t="s">
         <v>1323</v>
-      </c>
-      <c r="Q40" s="11" t="s">
-        <v>1324</v>
       </c>
       <c r="R40" s="11" t="s">
         <v>24</v>
@@ -10633,10 +10627,10 @@
         <v>1008</v>
       </c>
       <c r="W40" s="11" t="s">
+        <v>1324</v>
+      </c>
+      <c r="X40" s="11" t="s">
         <v>1325</v>
-      </c>
-      <c r="X40" s="11" t="s">
-        <v>1326</v>
       </c>
       <c r="Y40" s="11" t="s">
         <v>1133</v>
@@ -10645,25 +10639,25 @@
         <v>1133</v>
       </c>
       <c r="AA40" s="11" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="AB40" s="11" t="s">
         <v>1281</v>
       </c>
       <c r="AC40" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD40" s="11" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="AE40" s="11" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="AF40" s="11" t="s">
         <v>237</v>
       </c>
       <c r="AG40" s="11" t="s">
-        <v>1878</v>
+        <v>1875</v>
       </c>
       <c r="AH40" s="11" t="s">
         <v>26</v>
@@ -10675,7 +10669,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="41" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -10716,13 +10710,13 @@
         <v>1054</v>
       </c>
       <c r="O41" s="13" t="s">
+        <v>1345</v>
+      </c>
+      <c r="P41" s="13" t="s">
+        <v>1331</v>
+      </c>
+      <c r="Q41" s="13" t="s">
         <v>1346</v>
-      </c>
-      <c r="P41" s="13" t="s">
-        <v>1332</v>
-      </c>
-      <c r="Q41" s="13" t="s">
-        <v>1347</v>
       </c>
       <c r="R41" s="13" t="s">
         <v>24</v>
@@ -10737,40 +10731,40 @@
         <v>1146</v>
       </c>
       <c r="V41" s="13" t="s">
-        <v>1829</v>
+        <v>1827</v>
       </c>
       <c r="W41" s="13" t="s">
+        <v>1347</v>
+      </c>
+      <c r="X41" s="13" t="s">
         <v>1348</v>
-      </c>
-      <c r="X41" s="13" t="s">
-        <v>1349</v>
       </c>
       <c r="Y41" s="13" t="s">
         <v>1002</v>
       </c>
       <c r="Z41" s="13" t="s">
+        <v>1349</v>
+      </c>
+      <c r="AA41" s="13" t="s">
+        <v>1440</v>
+      </c>
+      <c r="AB41" s="13" t="s">
+        <v>1848</v>
+      </c>
+      <c r="AC41" s="13" t="s">
+        <v>1848</v>
+      </c>
+      <c r="AD41" s="13" t="s">
         <v>1350</v>
       </c>
-      <c r="AA41" s="13" t="s">
-        <v>1441</v>
-      </c>
-      <c r="AB41" s="13" t="s">
-        <v>1850</v>
-      </c>
-      <c r="AC41" s="13" t="s">
-        <v>1850</v>
-      </c>
-      <c r="AD41" s="13" t="s">
-        <v>1351</v>
-      </c>
       <c r="AE41" s="13" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="AF41" s="13" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG41" s="13" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH41" s="13" t="s">
         <v>26</v>
@@ -10782,7 +10776,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="42" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -10817,7 +10811,7 @@
         <v>236</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="M42" s="2" t="s">
         <v>1011</v>
@@ -10826,13 +10820,13 @@
         <v>994</v>
       </c>
       <c r="O42" s="13" t="s">
+        <v>1351</v>
+      </c>
+      <c r="P42" s="13" t="s">
         <v>1352</v>
       </c>
-      <c r="P42" s="13" t="s">
+      <c r="Q42" s="44" t="s">
         <v>1353</v>
-      </c>
-      <c r="Q42" s="44" t="s">
-        <v>1354</v>
       </c>
       <c r="R42" s="13" t="s">
         <v>24</v>
@@ -10844,55 +10838,55 @@
         <v>1122</v>
       </c>
       <c r="U42" s="13" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="V42" s="13" t="s">
         <v>1008</v>
       </c>
       <c r="W42" s="13" t="s">
+        <v>1355</v>
+      </c>
+      <c r="X42" s="13" t="s">
         <v>1356</v>
-      </c>
-      <c r="X42" s="13" t="s">
-        <v>1357</v>
       </c>
       <c r="Y42" s="13" t="s">
         <v>1002</v>
       </c>
       <c r="Z42" s="13" t="s">
+        <v>1357</v>
+      </c>
+      <c r="AA42" s="2" t="s">
+        <v>1842</v>
+      </c>
+      <c r="AB42" s="13" t="s">
+        <v>1848</v>
+      </c>
+      <c r="AC42" s="13" t="s">
+        <v>1916</v>
+      </c>
+      <c r="AD42" s="13" t="s">
         <v>1358</v>
       </c>
-      <c r="AA42" s="2" t="s">
-        <v>1844</v>
-      </c>
-      <c r="AB42" s="13" t="s">
-        <v>1850</v>
-      </c>
-      <c r="AC42" s="13" t="s">
-        <v>1919</v>
-      </c>
-      <c r="AD42" s="13" t="s">
+      <c r="AE42" s="13" t="s">
         <v>1359</v>
       </c>
-      <c r="AE42" s="13" t="s">
-        <v>1360</v>
-      </c>
       <c r="AF42" s="13" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG42" s="13" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH42" s="15" t="s">
         <v>1216</v>
       </c>
       <c r="AI42" s="15" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="AJ42" s="13" t="s">
         <v>1151</v>
       </c>
     </row>
-    <row r="43" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -10927,7 +10921,7 @@
         <v>335</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>1827</v>
+        <v>1825</v>
       </c>
       <c r="M43" s="2" t="s">
         <v>1011</v>
@@ -10936,13 +10930,13 @@
         <v>995</v>
       </c>
       <c r="O43" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="P43" s="13" t="s">
         <v>1362</v>
       </c>
-      <c r="P43" s="13" t="s">
+      <c r="Q43" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="Q43" s="44" t="s">
-        <v>1364</v>
       </c>
       <c r="R43" s="13" t="s">
         <v>24</v>
@@ -10960,37 +10954,37 @@
         <v>1008</v>
       </c>
       <c r="W43" s="13" t="s">
+        <v>1364</v>
+      </c>
+      <c r="X43" s="13" t="s">
         <v>1365</v>
       </c>
-      <c r="X43" s="13" t="s">
+      <c r="Y43" s="13" t="s">
         <v>1366</v>
       </c>
-      <c r="Y43" s="13" t="s">
+      <c r="Z43" s="13" t="s">
         <v>1367</v>
       </c>
-      <c r="Z43" s="13" t="s">
+      <c r="AA43" s="13" t="s">
+        <v>1842</v>
+      </c>
+      <c r="AB43" s="13" t="s">
         <v>1368</v>
       </c>
-      <c r="AA43" s="13" t="s">
-        <v>1844</v>
-      </c>
-      <c r="AB43" s="13" t="s">
+      <c r="AC43" s="13" t="s">
+        <v>1918</v>
+      </c>
+      <c r="AD43" s="13" t="s">
         <v>1369</v>
-      </c>
-      <c r="AC43" s="13" t="s">
-        <v>1921</v>
-      </c>
-      <c r="AD43" s="13" t="s">
-        <v>1370</v>
       </c>
       <c r="AE43" s="13" t="s">
         <v>1081</v>
       </c>
       <c r="AF43" s="13" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG43" s="13" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH43" s="13" t="s">
         <v>26</v>
@@ -11002,7 +10996,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="44" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -11043,13 +11037,13 @@
         <v>1054</v>
       </c>
       <c r="O44" s="13" t="s">
+        <v>1370</v>
+      </c>
+      <c r="P44" s="13" t="s">
         <v>1371</v>
       </c>
-      <c r="P44" s="13" t="s">
+      <c r="Q44" s="44" t="s">
         <v>1372</v>
-      </c>
-      <c r="Q44" s="44" t="s">
-        <v>1373</v>
       </c>
       <c r="R44" s="13" t="s">
         <v>24</v>
@@ -11067,37 +11061,37 @@
         <v>1008</v>
       </c>
       <c r="W44" s="13" t="s">
+        <v>1373</v>
+      </c>
+      <c r="X44" s="13" t="s">
         <v>1374</v>
-      </c>
-      <c r="X44" s="13" t="s">
-        <v>1375</v>
       </c>
       <c r="Y44" s="13" t="s">
         <v>1002</v>
       </c>
       <c r="Z44" s="13" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="AA44" s="13" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="AB44" s="13" t="s">
         <v>77</v>
       </c>
       <c r="AC44" s="13" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD44" s="13" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="AE44" s="13" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="AF44" s="13" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG44" s="13" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH44" s="13" t="s">
         <v>26</v>
@@ -11109,7 +11103,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="45" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -11147,16 +11141,16 @@
         <v>1011</v>
       </c>
       <c r="N45" s="16" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="O45" s="13" t="s">
+        <v>1377</v>
+      </c>
+      <c r="P45" s="13" t="s">
         <v>1378</v>
       </c>
-      <c r="P45" s="13" t="s">
+      <c r="Q45" s="44" t="s">
         <v>1379</v>
-      </c>
-      <c r="Q45" s="44" t="s">
-        <v>1380</v>
       </c>
       <c r="R45" s="13" t="s">
         <v>24</v>
@@ -11171,40 +11165,40 @@
         <v>1146</v>
       </c>
       <c r="V45" s="13" t="s">
+        <v>1380</v>
+      </c>
+      <c r="W45" s="13" t="s">
         <v>1381</v>
       </c>
-      <c r="W45" s="13" t="s">
+      <c r="X45" s="13" t="s">
         <v>1382</v>
       </c>
-      <c r="X45" s="13" t="s">
+      <c r="Y45" s="13" t="s">
         <v>1383</v>
-      </c>
-      <c r="Y45" s="13" t="s">
-        <v>1384</v>
       </c>
       <c r="Z45" s="13" t="s">
         <v>1133</v>
       </c>
       <c r="AA45" s="13" t="s">
-        <v>1848</v>
+        <v>1846</v>
       </c>
       <c r="AB45" s="13" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC45" s="13" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD45" s="13" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="AE45" s="13" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="AF45" s="13" t="s">
         <v>25</v>
       </c>
       <c r="AG45" s="13" t="s">
-        <v>1949</v>
+        <v>1946</v>
       </c>
       <c r="AH45" s="13" t="s">
         <v>26</v>
@@ -11216,7 +11210,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="46" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -11260,13 +11254,13 @@
         <v>994</v>
       </c>
       <c r="O46" s="18" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="P46" s="18" t="s">
         <v>1002</v>
       </c>
       <c r="Q46" s="46" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="R46" s="18" t="s">
         <v>24</v>
@@ -11284,37 +11278,37 @@
         <v>1008</v>
       </c>
       <c r="W46" s="18" t="s">
+        <v>1387</v>
+      </c>
+      <c r="X46" s="18" t="s">
         <v>1388</v>
       </c>
-      <c r="X46" s="18" t="s">
+      <c r="Y46" s="18" t="s">
         <v>1389</v>
-      </c>
-      <c r="Y46" s="18" t="s">
-        <v>1390</v>
       </c>
       <c r="Z46" s="18" t="s">
         <v>1133</v>
       </c>
       <c r="AA46" s="18" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="AB46" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC46" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD46" s="18" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="AE46" s="18" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="AF46" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG46" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH46" s="18" t="s">
         <v>26</v>
@@ -11326,7 +11320,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="47" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -11367,13 +11361,13 @@
         <v>994</v>
       </c>
       <c r="O47" s="18" t="s">
+        <v>1391</v>
+      </c>
+      <c r="P47" s="18" t="s">
         <v>1392</v>
       </c>
-      <c r="P47" s="18" t="s">
+      <c r="Q47" s="18" t="s">
         <v>1393</v>
-      </c>
-      <c r="Q47" s="18" t="s">
-        <v>1394</v>
       </c>
       <c r="R47" s="18" t="s">
         <v>24</v>
@@ -11382,7 +11376,7 @@
         <v>1013</v>
       </c>
       <c r="T47" s="18" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="U47" s="18" t="s">
         <v>1146</v>
@@ -11391,10 +11385,10 @@
         <v>1008</v>
       </c>
       <c r="W47" s="18" t="s">
+        <v>1395</v>
+      </c>
+      <c r="X47" s="18" t="s">
         <v>1396</v>
-      </c>
-      <c r="X47" s="18" t="s">
-        <v>1397</v>
       </c>
       <c r="Y47" s="18" t="s">
         <v>1133</v>
@@ -11406,22 +11400,22 @@
         <v>990</v>
       </c>
       <c r="AB47" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC47" s="18" t="s">
+        <v>1397</v>
+      </c>
+      <c r="AD47" s="18" t="s">
         <v>1398</v>
       </c>
-      <c r="AD47" s="18" t="s">
-        <v>1399</v>
-      </c>
       <c r="AE47" s="18" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="AF47" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG47" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH47" s="18" t="s">
         <v>26</v>
@@ -11433,7 +11427,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="48" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -11477,13 +11471,13 @@
         <v>1054</v>
       </c>
       <c r="O48" s="18" t="s">
+        <v>1399</v>
+      </c>
+      <c r="P48" s="18" t="s">
         <v>1400</v>
       </c>
-      <c r="P48" s="18" t="s">
+      <c r="Q48" s="18" t="s">
         <v>1401</v>
-      </c>
-      <c r="Q48" s="18" t="s">
-        <v>1402</v>
       </c>
       <c r="R48" s="18" t="s">
         <v>24</v>
@@ -11501,49 +11495,49 @@
         <v>1008</v>
       </c>
       <c r="W48" s="18" t="s">
+        <v>1402</v>
+      </c>
+      <c r="X48" s="18" t="s">
         <v>1403</v>
       </c>
-      <c r="X48" s="18" t="s">
+      <c r="Y48" s="18" t="s">
         <v>1404</v>
       </c>
-      <c r="Y48" s="18" t="s">
+      <c r="Z48" s="18" t="s">
         <v>1405</v>
       </c>
-      <c r="Z48" s="18" t="s">
-        <v>1406</v>
-      </c>
       <c r="AA48" s="18" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="AB48" s="18" t="s">
         <v>1229</v>
       </c>
       <c r="AC48" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD48" s="18" t="s">
+        <v>1406</v>
+      </c>
+      <c r="AE48" s="18" t="s">
         <v>1407</v>
-      </c>
-      <c r="AE48" s="18" t="s">
-        <v>1408</v>
       </c>
       <c r="AF48" s="18" t="s">
         <v>237</v>
       </c>
       <c r="AG48" s="18" t="s">
-        <v>1879</v>
+        <v>1876</v>
       </c>
       <c r="AH48" s="19" t="s">
         <v>1216</v>
       </c>
       <c r="AI48" s="19" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="AJ48" s="18" t="s">
         <v>1151</v>
       </c>
     </row>
-    <row r="49" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -11584,64 +11578,64 @@
         <v>1011</v>
       </c>
       <c r="N49" s="11" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="O49" s="18" t="s">
+        <v>1409</v>
+      </c>
+      <c r="P49" s="18" t="s">
         <v>1410</v>
       </c>
-      <c r="P49" s="18" t="s">
+      <c r="Q49" s="46" t="s">
         <v>1411</v>
-      </c>
-      <c r="Q49" s="46" t="s">
-        <v>1412</v>
       </c>
       <c r="R49" s="18" t="s">
         <v>24</v>
       </c>
       <c r="S49" s="18" t="s">
+        <v>1412</v>
+      </c>
+      <c r="T49" s="18" t="s">
+        <v>1394</v>
+      </c>
+      <c r="U49" s="18" t="s">
+        <v>1354</v>
+      </c>
+      <c r="V49" s="18" t="s">
         <v>1413</v>
       </c>
-      <c r="T49" s="18" t="s">
-        <v>1395</v>
-      </c>
-      <c r="U49" s="18" t="s">
-        <v>1355</v>
-      </c>
-      <c r="V49" s="18" t="s">
+      <c r="W49" s="18" t="s">
         <v>1414</v>
       </c>
-      <c r="W49" s="18" t="s">
+      <c r="X49" s="18" t="s">
         <v>1415</v>
       </c>
-      <c r="X49" s="18" t="s">
+      <c r="Y49" s="18" t="s">
         <v>1416</v>
       </c>
-      <c r="Y49" s="18" t="s">
+      <c r="Z49" s="18" t="s">
         <v>1417</v>
       </c>
-      <c r="Z49" s="18" t="s">
+      <c r="AA49" s="18" t="s">
+        <v>1846</v>
+      </c>
+      <c r="AB49" s="18" t="s">
+        <v>1848</v>
+      </c>
+      <c r="AC49" s="18" t="s">
+        <v>1848</v>
+      </c>
+      <c r="AD49" s="18" t="s">
         <v>1418</v>
       </c>
-      <c r="AA49" s="18" t="s">
-        <v>1848</v>
-      </c>
-      <c r="AB49" s="18" t="s">
-        <v>1850</v>
-      </c>
-      <c r="AC49" s="18" t="s">
-        <v>1850</v>
-      </c>
-      <c r="AD49" s="18" t="s">
+      <c r="AE49" s="18" t="s">
+        <v>1407</v>
+      </c>
+      <c r="AF49" s="18" t="s">
         <v>1419</v>
       </c>
-      <c r="AE49" s="18" t="s">
-        <v>1408</v>
-      </c>
-      <c r="AF49" s="18" t="s">
-        <v>1420</v>
-      </c>
       <c r="AG49" s="18" t="s">
-        <v>1934</v>
+        <v>1931</v>
       </c>
       <c r="AH49" s="18" t="s">
         <v>26</v>
@@ -11653,7 +11647,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="50" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -11697,13 +11691,13 @@
         <v>994</v>
       </c>
       <c r="O50" s="18" t="s">
+        <v>1420</v>
+      </c>
+      <c r="P50" s="18" t="s">
         <v>1421</v>
       </c>
-      <c r="P50" s="18" t="s">
+      <c r="Q50" s="18" t="s">
         <v>1422</v>
-      </c>
-      <c r="Q50" s="18" t="s">
-        <v>1423</v>
       </c>
       <c r="R50" s="18" t="s">
         <v>24</v>
@@ -11721,10 +11715,10 @@
         <v>1008</v>
       </c>
       <c r="W50" s="18" t="s">
+        <v>1423</v>
+      </c>
+      <c r="X50" s="18" t="s">
         <v>1424</v>
-      </c>
-      <c r="X50" s="18" t="s">
-        <v>1425</v>
       </c>
       <c r="Y50" s="18" t="s">
         <v>1133</v>
@@ -11733,25 +11727,25 @@
         <v>1133</v>
       </c>
       <c r="AA50" s="18" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="AB50" s="18" t="s">
         <v>77</v>
       </c>
       <c r="AC50" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD50" s="18" t="s">
+        <v>1425</v>
+      </c>
+      <c r="AE50" s="18" t="s">
+        <v>1873</v>
+      </c>
+      <c r="AF50" s="18" t="s">
         <v>1426</v>
       </c>
-      <c r="AE50" s="18" t="s">
-        <v>1876</v>
-      </c>
-      <c r="AF50" s="18" t="s">
-        <v>1427</v>
-      </c>
       <c r="AG50" s="18" t="s">
-        <v>1880</v>
+        <v>1877</v>
       </c>
       <c r="AH50" s="18" t="s">
         <v>26</v>
@@ -11763,7 +11757,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="51" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -11795,22 +11789,22 @@
         <v>395</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="M51" s="2" t="s">
         <v>1011</v>
       </c>
       <c r="N51" s="16" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="O51" s="16" t="s">
+        <v>1427</v>
+      </c>
+      <c r="P51" s="16" t="s">
         <v>1428</v>
       </c>
-      <c r="P51" s="16" t="s">
+      <c r="Q51" s="45" t="s">
         <v>1429</v>
-      </c>
-      <c r="Q51" s="45" t="s">
-        <v>1430</v>
       </c>
       <c r="R51" s="16" t="s">
         <v>24</v>
@@ -11828,10 +11822,10 @@
         <v>1008</v>
       </c>
       <c r="W51" s="16" t="s">
+        <v>1430</v>
+      </c>
+      <c r="X51" s="16" t="s">
         <v>1431</v>
-      </c>
-      <c r="X51" s="16" t="s">
-        <v>1432</v>
       </c>
       <c r="Y51" s="16" t="s">
         <v>1007</v>
@@ -11840,25 +11834,25 @@
         <v>1133</v>
       </c>
       <c r="AA51" s="16" t="s">
-        <v>1848</v>
+        <v>1846</v>
       </c>
       <c r="AB51" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC51" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD51" s="16" t="s">
+        <v>1432</v>
+      </c>
+      <c r="AE51" s="16" t="s">
+        <v>1957</v>
+      </c>
+      <c r="AF51" s="16" t="s">
+        <v>1942</v>
+      </c>
+      <c r="AG51" s="16" t="s">
         <v>1433</v>
-      </c>
-      <c r="AE51" s="16" t="s">
-        <v>1960</v>
-      </c>
-      <c r="AF51" s="16" t="s">
-        <v>1945</v>
-      </c>
-      <c r="AG51" s="16" t="s">
-        <v>1434</v>
       </c>
       <c r="AH51" s="16" t="s">
         <v>26</v>
@@ -11870,7 +11864,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="52" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -11911,13 +11905,13 @@
         <v>994</v>
       </c>
       <c r="O52" s="16" t="s">
+        <v>1434</v>
+      </c>
+      <c r="P52" s="16" t="s">
         <v>1435</v>
       </c>
-      <c r="P52" s="16" t="s">
+      <c r="Q52" s="45" t="s">
         <v>1436</v>
-      </c>
-      <c r="Q52" s="45" t="s">
-        <v>1437</v>
       </c>
       <c r="R52" s="16" t="s">
         <v>24</v>
@@ -11935,37 +11929,37 @@
         <v>1008</v>
       </c>
       <c r="W52" s="16" t="s">
+        <v>1437</v>
+      </c>
+      <c r="X52" s="16" t="s">
         <v>1438</v>
-      </c>
-      <c r="X52" s="16" t="s">
-        <v>1439</v>
       </c>
       <c r="Y52" s="16" t="s">
         <v>1007</v>
       </c>
       <c r="Z52" s="16" t="s">
+        <v>1439</v>
+      </c>
+      <c r="AA52" s="16" t="s">
         <v>1440</v>
       </c>
-      <c r="AA52" s="16" t="s">
-        <v>1441</v>
-      </c>
       <c r="AB52" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC52" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD52" s="16" t="s">
         <v>1171</v>
       </c>
       <c r="AE52" s="16" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="AF52" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG52" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH52" s="16" t="s">
         <v>26</v>
@@ -11977,7 +11971,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="53" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -12015,16 +12009,16 @@
         <v>993</v>
       </c>
       <c r="N53" s="16" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="O53" s="16" t="s">
+        <v>1441</v>
+      </c>
+      <c r="P53" s="16" t="s">
         <v>1442</v>
       </c>
-      <c r="P53" s="16" t="s">
+      <c r="Q53" s="16" t="s">
         <v>1443</v>
-      </c>
-      <c r="Q53" s="16" t="s">
-        <v>1444</v>
       </c>
       <c r="R53" s="16" t="s">
         <v>24</v>
@@ -12042,37 +12036,37 @@
         <v>1008</v>
       </c>
       <c r="W53" s="16" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="X53" s="16" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="Y53" s="16" t="s">
         <v>1007</v>
       </c>
       <c r="Z53" s="16" t="s">
+        <v>1445</v>
+      </c>
+      <c r="AA53" s="16" t="s">
+        <v>1844</v>
+      </c>
+      <c r="AB53" s="16" t="s">
+        <v>1848</v>
+      </c>
+      <c r="AC53" s="16" t="s">
+        <v>1848</v>
+      </c>
+      <c r="AD53" s="16" t="s">
         <v>1446</v>
       </c>
-      <c r="AA53" s="16" t="s">
-        <v>1846</v>
-      </c>
-      <c r="AB53" s="16" t="s">
-        <v>1850</v>
-      </c>
-      <c r="AC53" s="16" t="s">
-        <v>1850</v>
-      </c>
-      <c r="AD53" s="16" t="s">
-        <v>1447</v>
-      </c>
       <c r="AE53" s="16" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="AF53" s="16" t="s">
         <v>25</v>
       </c>
       <c r="AG53" s="16" t="s">
-        <v>1908</v>
+        <v>1905</v>
       </c>
       <c r="AH53" s="16" t="s">
         <v>26</v>
@@ -12084,7 +12078,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="54" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -12128,13 +12122,13 @@
         <v>981</v>
       </c>
       <c r="O54" s="16" t="s">
+        <v>1448</v>
+      </c>
+      <c r="P54" s="16" t="s">
         <v>1449</v>
       </c>
-      <c r="P54" s="16" t="s">
+      <c r="Q54" s="16" t="s">
         <v>1450</v>
-      </c>
-      <c r="Q54" s="16" t="s">
-        <v>1451</v>
       </c>
       <c r="R54" s="16" t="s">
         <v>24</v>
@@ -12152,49 +12146,49 @@
         <v>1008</v>
       </c>
       <c r="W54" s="16" t="s">
+        <v>1451</v>
+      </c>
+      <c r="X54" s="16" t="s">
+        <v>1437</v>
+      </c>
+      <c r="Y54" s="16" t="s">
         <v>1452</v>
       </c>
-      <c r="X54" s="16" t="s">
-        <v>1438</v>
-      </c>
-      <c r="Y54" s="16" t="s">
-        <v>1453</v>
-      </c>
       <c r="Z54" s="16" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="AA54" s="16" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="AB54" s="16" t="s">
         <v>77</v>
       </c>
       <c r="AC54" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD54" s="16" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="AE54" s="16" t="s">
-        <v>1961</v>
+        <v>1958</v>
       </c>
       <c r="AF54" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG54" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH54" s="16" t="s">
         <v>1216</v>
       </c>
       <c r="AI54" s="16" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="AJ54" s="16" t="s">
         <v>1151</v>
       </c>
     </row>
-    <row r="55" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -12238,13 +12232,13 @@
         <v>995</v>
       </c>
       <c r="O55" s="18" t="s">
+        <v>1455</v>
+      </c>
+      <c r="P55" s="18" t="s">
         <v>1456</v>
       </c>
-      <c r="P55" s="18" t="s">
+      <c r="Q55" s="18" t="s">
         <v>1457</v>
-      </c>
-      <c r="Q55" s="18" t="s">
-        <v>1458</v>
       </c>
       <c r="R55" s="18" t="s">
         <v>24</v>
@@ -12262,37 +12256,37 @@
         <v>1008</v>
       </c>
       <c r="W55" s="18" t="s">
+        <v>1458</v>
+      </c>
+      <c r="X55" s="18" t="s">
+        <v>1438</v>
+      </c>
+      <c r="Y55" s="18" t="s">
         <v>1459</v>
       </c>
-      <c r="X55" s="18" t="s">
-        <v>1439</v>
-      </c>
-      <c r="Y55" s="18" t="s">
+      <c r="Z55" s="18" t="s">
         <v>1460</v>
       </c>
-      <c r="Z55" s="18" t="s">
-        <v>1461</v>
-      </c>
       <c r="AA55" s="18" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AB55" s="18" t="s">
         <v>77</v>
       </c>
       <c r="AC55" s="18" t="s">
-        <v>1843</v>
+        <v>1841</v>
       </c>
       <c r="AD55" s="18" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="AE55" s="18" t="s">
         <v>997</v>
       </c>
       <c r="AF55" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG55" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH55" s="18" t="s">
         <v>26</v>
@@ -12304,7 +12298,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="56" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -12348,13 +12342,13 @@
         <v>1054</v>
       </c>
       <c r="O56" s="18" t="s">
+        <v>1462</v>
+      </c>
+      <c r="P56" s="18" t="s">
         <v>1463</v>
       </c>
-      <c r="P56" s="18" t="s">
+      <c r="Q56" s="18" t="s">
         <v>1464</v>
-      </c>
-      <c r="Q56" s="18" t="s">
-        <v>1465</v>
       </c>
       <c r="R56" s="18" t="s">
         <v>24</v>
@@ -12372,49 +12366,49 @@
         <v>1008</v>
       </c>
       <c r="W56" s="18" t="s">
+        <v>1465</v>
+      </c>
+      <c r="X56" s="18" t="s">
+        <v>1438</v>
+      </c>
+      <c r="Y56" s="18" t="s">
+        <v>1459</v>
+      </c>
+      <c r="Z56" s="18" t="s">
         <v>1466</v>
       </c>
-      <c r="X56" s="18" t="s">
-        <v>1439</v>
-      </c>
-      <c r="Y56" s="18" t="s">
-        <v>1460</v>
-      </c>
-      <c r="Z56" s="18" t="s">
-        <v>1467</v>
-      </c>
       <c r="AA56" s="18" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AB56" s="18" t="s">
         <v>77</v>
       </c>
       <c r="AC56" s="18" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="AD56" s="18" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="AE56" s="18" t="s">
         <v>1028</v>
       </c>
       <c r="AF56" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG56" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH56" s="19" t="s">
         <v>1216</v>
       </c>
       <c r="AI56" s="19" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="AJ56" s="18" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="57" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -12458,13 +12452,13 @@
         <v>994</v>
       </c>
       <c r="O57" s="18" t="s">
+        <v>1469</v>
+      </c>
+      <c r="P57" s="18" t="s">
         <v>1470</v>
       </c>
-      <c r="P57" s="18" t="s">
+      <c r="Q57" s="18" t="s">
         <v>1471</v>
-      </c>
-      <c r="Q57" s="18" t="s">
-        <v>1472</v>
       </c>
       <c r="R57" s="18" t="s">
         <v>24</v>
@@ -12479,48 +12473,48 @@
         <v>1146</v>
       </c>
       <c r="V57" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="W57" s="18" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="X57" s="18" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="Y57" s="18"/>
       <c r="Z57" s="18"/>
       <c r="AA57" s="18" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AB57" s="18" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="AC57" s="18" t="s">
-        <v>1911</v>
+        <v>1908</v>
       </c>
       <c r="AD57" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AE57" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AF57" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AG57" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AH57" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AI57" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AJ57" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
     </row>
-    <row r="58" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -12561,13 +12555,13 @@
         <v>994</v>
       </c>
       <c r="O58" s="18" t="s">
+        <v>1473</v>
+      </c>
+      <c r="P58" s="18" t="s">
         <v>1474</v>
       </c>
-      <c r="P58" s="18" t="s">
+      <c r="Q58" s="46" t="s">
         <v>1475</v>
-      </c>
-      <c r="Q58" s="46" t="s">
-        <v>1476</v>
       </c>
       <c r="R58" s="18" t="s">
         <v>24</v>
@@ -12585,37 +12579,37 @@
         <v>1008</v>
       </c>
       <c r="W58" s="18" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="X58" s="18" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Y58" s="18" t="s">
         <v>1133</v>
       </c>
       <c r="Z58" s="18" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="AA58" s="18" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="AB58" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC58" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD58" s="18" t="s">
         <v>1130</v>
       </c>
       <c r="AE58" s="18" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="AF58" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG58" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH58" s="18" t="s">
         <v>26</v>
@@ -12627,7 +12621,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="59" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -12671,13 +12665,13 @@
         <v>995</v>
       </c>
       <c r="O59" s="18" t="s">
+        <v>1477</v>
+      </c>
+      <c r="P59" s="18" t="s">
         <v>1478</v>
       </c>
-      <c r="P59" s="18" t="s">
+      <c r="Q59" s="46" t="s">
         <v>1479</v>
-      </c>
-      <c r="Q59" s="46" t="s">
-        <v>1480</v>
       </c>
       <c r="R59" s="18" t="s">
         <v>24</v>
@@ -12695,49 +12689,49 @@
         <v>1008</v>
       </c>
       <c r="W59" s="18" t="s">
+        <v>1480</v>
+      </c>
+      <c r="X59" s="18" t="s">
         <v>1481</v>
       </c>
-      <c r="X59" s="18" t="s">
+      <c r="Y59" s="18" t="s">
+        <v>1459</v>
+      </c>
+      <c r="Z59" s="18" t="s">
         <v>1482</v>
       </c>
-      <c r="Y59" s="18" t="s">
-        <v>1460</v>
-      </c>
-      <c r="Z59" s="18" t="s">
+      <c r="AA59" s="18" t="s">
+        <v>1842</v>
+      </c>
+      <c r="AB59" s="18" t="s">
         <v>1483</v>
       </c>
-      <c r="AA59" s="18" t="s">
-        <v>1844</v>
-      </c>
-      <c r="AB59" s="18" t="s">
+      <c r="AC59" s="18" t="s">
+        <v>1919</v>
+      </c>
+      <c r="AD59" s="18" t="s">
         <v>1484</v>
-      </c>
-      <c r="AC59" s="18" t="s">
-        <v>1922</v>
-      </c>
-      <c r="AD59" s="18" t="s">
-        <v>1485</v>
       </c>
       <c r="AE59" s="18" t="s">
         <v>1081</v>
       </c>
       <c r="AF59" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG59" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH59" s="19" t="s">
         <v>1216</v>
       </c>
       <c r="AI59" s="19" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="AJ59" s="18" t="s">
         <v>1151</v>
       </c>
     </row>
-    <row r="60" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -12778,16 +12772,16 @@
         <v>993</v>
       </c>
       <c r="N60" s="16" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="O60" s="16" t="s">
+        <v>1486</v>
+      </c>
+      <c r="P60" s="16" t="s">
         <v>1487</v>
       </c>
-      <c r="P60" s="16" t="s">
+      <c r="Q60" s="16" t="s">
         <v>1488</v>
-      </c>
-      <c r="Q60" s="16" t="s">
-        <v>1489</v>
       </c>
       <c r="R60" s="16" t="s">
         <v>24</v>
@@ -12802,48 +12796,48 @@
         <v>1146</v>
       </c>
       <c r="V60" s="16" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="W60" s="16" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="X60" s="16" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="Y60" s="16"/>
       <c r="Z60" s="16"/>
       <c r="AA60" s="16" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="AB60" s="16" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="AC60" s="16" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AD60" s="16" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AE60" s="16" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AF60" s="16" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AG60" s="16" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AH60" s="16" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AI60" s="16" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AJ60" s="16" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
     </row>
-    <row r="61" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -12881,16 +12875,16 @@
         <v>1011</v>
       </c>
       <c r="N61" s="16" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="O61" s="16" t="s">
+        <v>1490</v>
+      </c>
+      <c r="P61" s="16" t="s">
         <v>1491</v>
       </c>
-      <c r="P61" s="16" t="s">
+      <c r="Q61" s="45" t="s">
         <v>1492</v>
-      </c>
-      <c r="Q61" s="45" t="s">
-        <v>1493</v>
       </c>
       <c r="R61" s="16" t="s">
         <v>24</v>
@@ -12908,37 +12902,37 @@
         <v>1008</v>
       </c>
       <c r="W61" s="16" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="X61" s="16" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="Y61" s="16" t="s">
         <v>1133</v>
       </c>
       <c r="Z61" s="16" t="s">
+        <v>1494</v>
+      </c>
+      <c r="AA61" s="16" t="s">
+        <v>1842</v>
+      </c>
+      <c r="AB61" s="16" t="s">
+        <v>1848</v>
+      </c>
+      <c r="AC61" s="16" t="s">
+        <v>1832</v>
+      </c>
+      <c r="AD61" s="16" t="s">
         <v>1495</v>
       </c>
-      <c r="AA61" s="16" t="s">
-        <v>1844</v>
-      </c>
-      <c r="AB61" s="16" t="s">
-        <v>1850</v>
-      </c>
-      <c r="AC61" s="16" t="s">
-        <v>1834</v>
-      </c>
-      <c r="AD61" s="16" t="s">
-        <v>1496</v>
-      </c>
       <c r="AE61" s="16" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="AF61" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG61" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH61" s="16" t="s">
         <v>26</v>
@@ -12950,7 +12944,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="62" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -12985,7 +12979,7 @@
         <v>236</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="M62" s="2" t="s">
         <v>993</v>
@@ -12994,13 +12988,13 @@
         <v>1054</v>
       </c>
       <c r="O62" s="16" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="P62" s="16" t="s">
         <v>1068</v>
       </c>
       <c r="Q62" s="16" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="R62" s="16" t="s">
         <v>24</v>
@@ -13018,37 +13012,37 @@
         <v>1008</v>
       </c>
       <c r="W62" s="16" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="X62" s="16" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="Y62" s="16" t="s">
         <v>1265</v>
       </c>
       <c r="Z62" s="16" t="s">
+        <v>1499</v>
+      </c>
+      <c r="AA62" s="16" t="s">
+        <v>1842</v>
+      </c>
+      <c r="AB62" s="16" t="s">
         <v>1500</v>
       </c>
-      <c r="AA62" s="16" t="s">
-        <v>1844</v>
-      </c>
-      <c r="AB62" s="16" t="s">
+      <c r="AC62" s="16" t="s">
+        <v>1912</v>
+      </c>
+      <c r="AD62" s="16" t="s">
         <v>1501</v>
-      </c>
-      <c r="AC62" s="16" t="s">
-        <v>1915</v>
-      </c>
-      <c r="AD62" s="16" t="s">
-        <v>1502</v>
       </c>
       <c r="AE62" s="16" t="s">
         <v>996</v>
       </c>
       <c r="AF62" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG62" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH62" s="16" t="s">
         <v>26</v>
@@ -13060,7 +13054,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="63" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -13104,13 +13098,13 @@
         <v>995</v>
       </c>
       <c r="O63" s="16" t="s">
+        <v>1502</v>
+      </c>
+      <c r="P63" s="16" t="s">
         <v>1503</v>
       </c>
-      <c r="P63" s="16" t="s">
+      <c r="Q63" s="45" t="s">
         <v>1504</v>
-      </c>
-      <c r="Q63" s="45" t="s">
-        <v>1505</v>
       </c>
       <c r="R63" s="16" t="s">
         <v>24</v>
@@ -13128,37 +13122,37 @@
         <v>1008</v>
       </c>
       <c r="W63" s="16" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="X63" s="16" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="Y63" s="16" t="s">
+        <v>1505</v>
+      </c>
+      <c r="Z63" s="16" t="s">
         <v>1506</v>
       </c>
-      <c r="Z63" s="16" t="s">
-        <v>1507</v>
-      </c>
       <c r="AA63" s="16" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="AB63" s="16" t="s">
         <v>62</v>
       </c>
       <c r="AC63" s="16" t="s">
-        <v>1835</v>
+        <v>1833</v>
       </c>
       <c r="AD63" s="16" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="AE63" s="16" t="s">
         <v>997</v>
       </c>
       <c r="AF63" s="16" t="s">
-        <v>1943</v>
+        <v>1940</v>
       </c>
       <c r="AG63" s="16" t="s">
-        <v>1860</v>
+        <v>1857</v>
       </c>
       <c r="AH63" s="16" t="s">
         <v>26</v>
@@ -13170,7 +13164,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="64" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>63</v>
       </c>
@@ -13205,7 +13199,7 @@
         <v>236</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="M64" s="2" t="s">
         <v>993</v>
@@ -13214,13 +13208,13 @@
         <v>995</v>
       </c>
       <c r="O64" s="16" t="s">
+        <v>1508</v>
+      </c>
+      <c r="P64" s="16" t="s">
         <v>1509</v>
       </c>
-      <c r="P64" s="16" t="s">
+      <c r="Q64" s="16" t="s">
         <v>1510</v>
-      </c>
-      <c r="Q64" s="16" t="s">
-        <v>1511</v>
       </c>
       <c r="R64" s="16" t="s">
         <v>24</v>
@@ -13238,28 +13232,28 @@
         <v>1008</v>
       </c>
       <c r="W64" s="16" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="X64" s="16" t="s">
+        <v>1511</v>
+      </c>
+      <c r="Y64" s="16" t="s">
+        <v>1459</v>
+      </c>
+      <c r="Z64" s="16" t="s">
         <v>1512</v>
       </c>
-      <c r="Y64" s="16" t="s">
-        <v>1460</v>
-      </c>
-      <c r="Z64" s="16" t="s">
-        <v>1513</v>
-      </c>
       <c r="AA64" s="16" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="AB64" s="16" t="s">
         <v>54</v>
       </c>
       <c r="AC64" s="16" t="s">
-        <v>1841</v>
+        <v>1839</v>
       </c>
       <c r="AD64" s="16" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="AE64" s="16" t="s">
         <v>1132</v>
@@ -13268,19 +13262,19 @@
         <v>237</v>
       </c>
       <c r="AG64" s="16" t="s">
-        <v>1861</v>
+        <v>1858</v>
       </c>
       <c r="AH64" s="17" t="s">
         <v>1216</v>
       </c>
       <c r="AI64" s="17" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="AJ64" s="16" t="s">
         <v>1151</v>
       </c>
     </row>
-    <row r="65" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>64</v>
       </c>
@@ -13321,13 +13315,13 @@
         <v>994</v>
       </c>
       <c r="O65" s="18" t="s">
+        <v>1515</v>
+      </c>
+      <c r="P65" s="18" t="s">
         <v>1516</v>
       </c>
-      <c r="P65" s="18" t="s">
+      <c r="Q65" s="46" t="s">
         <v>1517</v>
-      </c>
-      <c r="Q65" s="46" t="s">
-        <v>1518</v>
       </c>
       <c r="R65" s="18" t="s">
         <v>24</v>
@@ -13345,10 +13339,10 @@
         <v>1008</v>
       </c>
       <c r="W65" s="18" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="X65" s="18" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Y65" s="18" t="s">
         <v>26</v>
@@ -13357,25 +13351,25 @@
         <v>26</v>
       </c>
       <c r="AA65" s="18" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="AB65" s="18" t="s">
         <v>77</v>
       </c>
       <c r="AC65" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD65" s="18" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="AE65" s="18" t="s">
         <v>996</v>
       </c>
       <c r="AF65" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG65" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH65" s="18" t="s">
         <v>26</v>
@@ -13387,7 +13381,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="66" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>65</v>
       </c>
@@ -13431,13 +13425,13 @@
         <v>1054</v>
       </c>
       <c r="O66" s="18" t="s">
+        <v>1519</v>
+      </c>
+      <c r="P66" s="18" t="s">
         <v>1520</v>
       </c>
-      <c r="P66" s="18" t="s">
+      <c r="Q66" s="18" t="s">
         <v>1521</v>
-      </c>
-      <c r="Q66" s="18" t="s">
-        <v>1522</v>
       </c>
       <c r="R66" s="18" t="s">
         <v>24</v>
@@ -13455,49 +13449,49 @@
         <v>1008</v>
       </c>
       <c r="W66" s="18" t="s">
+        <v>1522</v>
+      </c>
+      <c r="X66" s="18" t="s">
+        <v>1438</v>
+      </c>
+      <c r="Y66" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z66" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA66" s="18" t="s">
+        <v>1440</v>
+      </c>
+      <c r="AB66" s="18" t="s">
+        <v>1848</v>
+      </c>
+      <c r="AC66" s="18" t="s">
+        <v>1848</v>
+      </c>
+      <c r="AD66" s="18" t="s">
         <v>1523</v>
-      </c>
-      <c r="X66" s="18" t="s">
-        <v>1439</v>
-      </c>
-      <c r="Y66" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z66" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA66" s="18" t="s">
-        <v>1441</v>
-      </c>
-      <c r="AB66" s="18" t="s">
-        <v>1850</v>
-      </c>
-      <c r="AC66" s="18" t="s">
-        <v>1850</v>
-      </c>
-      <c r="AD66" s="18" t="s">
-        <v>1524</v>
       </c>
       <c r="AE66" s="18" t="s">
         <v>997</v>
       </c>
       <c r="AF66" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG66" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH66" s="19" t="s">
         <v>1216</v>
       </c>
       <c r="AI66" s="19" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="AJ66" s="18" t="s">
         <v>1151</v>
       </c>
     </row>
-    <row r="67" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>66</v>
       </c>
@@ -13538,13 +13532,13 @@
         <v>1054</v>
       </c>
       <c r="O67" s="18" t="s">
+        <v>1525</v>
+      </c>
+      <c r="P67" s="18" t="s">
         <v>1526</v>
       </c>
-      <c r="P67" s="18" t="s">
+      <c r="Q67" s="46" t="s">
         <v>1527</v>
-      </c>
-      <c r="Q67" s="46" t="s">
-        <v>1528</v>
       </c>
       <c r="R67" s="18" t="s">
         <v>24</v>
@@ -13562,49 +13556,49 @@
         <v>1008</v>
       </c>
       <c r="W67" s="18" t="s">
+        <v>1528</v>
+      </c>
+      <c r="X67" s="18" t="s">
         <v>1529</v>
       </c>
-      <c r="X67" s="18" t="s">
+      <c r="Y67" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z67" s="18" t="s">
+        <v>1447</v>
+      </c>
+      <c r="AA67" s="18" t="s">
+        <v>1842</v>
+      </c>
+      <c r="AB67" s="18" t="s">
         <v>1530</v>
       </c>
-      <c r="Y67" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z67" s="18" t="s">
-        <v>1448</v>
-      </c>
-      <c r="AA67" s="18" t="s">
-        <v>1844</v>
-      </c>
-      <c r="AB67" s="18" t="s">
+      <c r="AC67" s="18" t="s">
         <v>1531</v>
       </c>
-      <c r="AC67" s="18" t="s">
+      <c r="AD67" s="18" t="s">
         <v>1532</v>
       </c>
-      <c r="AD67" s="18" t="s">
-        <v>1533</v>
-      </c>
       <c r="AE67" s="18" t="s">
-        <v>1965</v>
+        <v>1962</v>
       </c>
       <c r="AF67" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG67" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH67" s="19" t="s">
         <v>1216</v>
       </c>
       <c r="AI67" s="19" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="AJ67" s="18" t="s">
         <v>1151</v>
       </c>
     </row>
-    <row r="68" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>67</v>
       </c>
@@ -13639,22 +13633,22 @@
         <v>335</v>
       </c>
       <c r="L68" s="4" t="s">
-        <v>1827</v>
+        <v>1825</v>
       </c>
       <c r="M68" s="4" t="s">
         <v>1011</v>
       </c>
       <c r="N68" s="18" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="O68" s="18" t="s">
+        <v>1534</v>
+      </c>
+      <c r="P68" s="18" t="s">
         <v>1535</v>
       </c>
-      <c r="P68" s="18" t="s">
+      <c r="Q68" s="46" t="s">
         <v>1536</v>
-      </c>
-      <c r="Q68" s="46" t="s">
-        <v>1537</v>
       </c>
       <c r="R68" s="18" t="s">
         <v>24</v>
@@ -13672,37 +13666,37 @@
         <v>1008</v>
       </c>
       <c r="W68" s="18" t="s">
+        <v>1537</v>
+      </c>
+      <c r="X68" s="18" t="s">
         <v>1538</v>
       </c>
-      <c r="X68" s="18" t="s">
+      <c r="Y68" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z68" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA68" s="18" t="s">
+        <v>1842</v>
+      </c>
+      <c r="AB68" s="18" t="s">
+        <v>1848</v>
+      </c>
+      <c r="AC68" s="18" t="s">
+        <v>1891</v>
+      </c>
+      <c r="AD68" s="18" t="s">
         <v>1539</v>
-      </c>
-      <c r="Y68" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z68" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA68" s="18" t="s">
-        <v>1844</v>
-      </c>
-      <c r="AB68" s="18" t="s">
-        <v>1850</v>
-      </c>
-      <c r="AC68" s="18" t="s">
-        <v>1894</v>
-      </c>
-      <c r="AD68" s="18" t="s">
-        <v>1540</v>
       </c>
       <c r="AE68" s="18" t="s">
         <v>996</v>
       </c>
       <c r="AF68" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG68" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH68" s="18" t="s">
         <v>26</v>
@@ -13714,7 +13708,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="69" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -13752,16 +13746,16 @@
         <v>1011</v>
       </c>
       <c r="N69" s="18" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="O69" s="18" t="s">
+        <v>1540</v>
+      </c>
+      <c r="P69" s="18" t="s">
         <v>1541</v>
       </c>
-      <c r="P69" s="18" t="s">
+      <c r="Q69" s="46" t="s">
         <v>1542</v>
-      </c>
-      <c r="Q69" s="46" t="s">
-        <v>1543</v>
       </c>
       <c r="R69" s="18" t="s">
         <v>24</v>
@@ -13779,37 +13773,37 @@
         <v>1008</v>
       </c>
       <c r="W69" s="18" t="s">
+        <v>1543</v>
+      </c>
+      <c r="X69" s="18" t="s">
         <v>1544</v>
       </c>
-      <c r="X69" s="18" t="s">
+      <c r="Y69" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z69" s="18" t="s">
         <v>1545</v>
       </c>
-      <c r="Y69" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z69" s="18" t="s">
-        <v>1546</v>
-      </c>
       <c r="AA69" s="18" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="AB69" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC69" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD69" s="18" t="s">
         <v>1171</v>
       </c>
       <c r="AE69" s="18" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="AF69" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG69" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH69" s="18" t="s">
         <v>26</v>
@@ -13821,7 +13815,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="70" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>69</v>
       </c>
@@ -13862,19 +13856,19 @@
         <v>981</v>
       </c>
       <c r="O70" s="16" t="s">
+        <v>1546</v>
+      </c>
+      <c r="P70" s="16" t="s">
         <v>1547</v>
       </c>
-      <c r="P70" s="16" t="s">
+      <c r="Q70" s="45" t="s">
         <v>1548</v>
-      </c>
-      <c r="Q70" s="45" t="s">
-        <v>1549</v>
       </c>
       <c r="R70" s="16" t="s">
         <v>24</v>
       </c>
       <c r="S70" s="16" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="T70" s="16" t="s">
         <v>1122</v>
@@ -13886,49 +13880,49 @@
         <v>1008</v>
       </c>
       <c r="W70" s="16" t="s">
+        <v>1550</v>
+      </c>
+      <c r="X70" s="16" t="s">
         <v>1551</v>
-      </c>
-      <c r="X70" s="16" t="s">
-        <v>1552</v>
       </c>
       <c r="Y70" s="16" t="s">
         <v>1007</v>
       </c>
       <c r="Z70" s="16" t="s">
+        <v>1552</v>
+      </c>
+      <c r="AA70" s="16" t="s">
+        <v>1845</v>
+      </c>
+      <c r="AB70" s="16" t="s">
         <v>1553</v>
       </c>
-      <c r="AA70" s="16" t="s">
-        <v>1847</v>
-      </c>
-      <c r="AB70" s="16" t="s">
+      <c r="AC70" s="16" t="s">
         <v>1554</v>
       </c>
-      <c r="AC70" s="16" t="s">
+      <c r="AD70" s="16" t="s">
         <v>1555</v>
-      </c>
-      <c r="AD70" s="16" t="s">
-        <v>1556</v>
       </c>
       <c r="AE70" s="16" t="s">
         <v>996</v>
       </c>
       <c r="AF70" s="16" t="s">
-        <v>1944</v>
+        <v>1941</v>
       </c>
       <c r="AG70" s="16" t="s">
-        <v>1864</v>
+        <v>1861</v>
       </c>
       <c r="AH70" s="17" t="s">
         <v>1216</v>
       </c>
       <c r="AI70" s="17" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="AJ70" s="16" t="s">
         <v>1151</v>
       </c>
     </row>
-    <row r="71" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>70</v>
       </c>
@@ -13960,7 +13954,7 @@
         <v>395</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="M71" s="2" t="s">
         <v>1011</v>
@@ -13969,19 +13963,19 @@
         <v>981</v>
       </c>
       <c r="O71" s="16" t="s">
+        <v>1557</v>
+      </c>
+      <c r="P71" s="16" t="s">
         <v>1558</v>
       </c>
-      <c r="P71" s="16" t="s">
+      <c r="Q71" s="45" t="s">
         <v>1559</v>
-      </c>
-      <c r="Q71" s="45" t="s">
-        <v>1560</v>
       </c>
       <c r="R71" s="16" t="s">
         <v>24</v>
       </c>
       <c r="S71" s="16" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="T71" s="16" t="s">
         <v>1122</v>
@@ -13990,40 +13984,40 @@
         <v>1146</v>
       </c>
       <c r="V71" s="16" t="s">
+        <v>1561</v>
+      </c>
+      <c r="W71" s="16" t="s">
         <v>1562</v>
       </c>
-      <c r="W71" s="16" t="s">
+      <c r="X71" s="16" t="s">
         <v>1563</v>
       </c>
-      <c r="X71" s="16" t="s">
+      <c r="Y71" s="16" t="s">
         <v>1564</v>
       </c>
-      <c r="Y71" s="16" t="s">
+      <c r="Z71" s="16" t="s">
         <v>1565</v>
       </c>
-      <c r="Z71" s="16" t="s">
+      <c r="AA71" s="16" t="s">
+        <v>1842</v>
+      </c>
+      <c r="AB71" s="16" t="s">
+        <v>1848</v>
+      </c>
+      <c r="AC71" s="16" t="s">
+        <v>1834</v>
+      </c>
+      <c r="AD71" s="16" t="s">
         <v>1566</v>
-      </c>
-      <c r="AA71" s="16" t="s">
-        <v>1844</v>
-      </c>
-      <c r="AB71" s="16" t="s">
-        <v>1850</v>
-      </c>
-      <c r="AC71" s="16" t="s">
-        <v>1836</v>
-      </c>
-      <c r="AD71" s="16" t="s">
-        <v>1567</v>
       </c>
       <c r="AE71" s="16" t="s">
         <v>1081</v>
       </c>
       <c r="AF71" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG71" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH71" s="16" t="s">
         <v>26</v>
@@ -14032,10 +14026,10 @@
         <v>26</v>
       </c>
       <c r="AJ71" s="16" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
     </row>
-    <row r="72" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>71</v>
       </c>
@@ -14076,19 +14070,19 @@
         <v>995</v>
       </c>
       <c r="O72" s="16" t="s">
+        <v>1568</v>
+      </c>
+      <c r="P72" s="16" t="s">
         <v>1569</v>
       </c>
-      <c r="P72" s="16" t="s">
+      <c r="Q72" s="45" t="s">
         <v>1570</v>
-      </c>
-      <c r="Q72" s="45" t="s">
-        <v>1571</v>
       </c>
       <c r="R72" s="16" t="s">
         <v>24</v>
       </c>
       <c r="S72" s="16" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="T72" s="16" t="s">
         <v>1122</v>
@@ -14100,37 +14094,37 @@
         <v>1008</v>
       </c>
       <c r="W72" s="16" t="s">
+        <v>1571</v>
+      </c>
+      <c r="X72" s="16" t="s">
         <v>1572</v>
-      </c>
-      <c r="X72" s="16" t="s">
-        <v>1573</v>
       </c>
       <c r="Y72" s="16" t="s">
         <v>1007</v>
       </c>
       <c r="Z72" s="16" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="AA72" s="16" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AB72" s="16" t="s">
         <v>62</v>
       </c>
       <c r="AC72" s="16" t="s">
-        <v>1926</v>
+        <v>1923</v>
       </c>
       <c r="AD72" s="16" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="AE72" s="16" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="AF72" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG72" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH72" s="16" t="s">
         <v>26</v>
@@ -14142,7 +14136,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="73" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>72</v>
       </c>
@@ -14186,73 +14180,73 @@
         <v>1054</v>
       </c>
       <c r="O73" s="16" t="s">
+        <v>1575</v>
+      </c>
+      <c r="P73" s="16" t="s">
         <v>1576</v>
       </c>
-      <c r="P73" s="16" t="s">
+      <c r="Q73" s="45" t="s">
         <v>1577</v>
-      </c>
-      <c r="Q73" s="45" t="s">
-        <v>1578</v>
       </c>
       <c r="R73" s="16" t="s">
         <v>24</v>
       </c>
       <c r="S73" s="16" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="T73" s="16" t="s">
         <v>1122</v>
       </c>
       <c r="U73" s="16" t="s">
+        <v>1578</v>
+      </c>
+      <c r="V73" s="16" t="s">
+        <v>1820</v>
+      </c>
+      <c r="W73" s="16" t="s">
         <v>1579</v>
       </c>
-      <c r="V73" s="16" t="s">
-        <v>1822</v>
-      </c>
-      <c r="W73" s="16" t="s">
+      <c r="X73" s="16" t="s">
         <v>1580</v>
       </c>
-      <c r="X73" s="16" t="s">
-        <v>1581</v>
-      </c>
       <c r="Y73" s="16" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="Z73" s="16" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AA73" s="16" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="AB73" s="16" t="s">
         <v>77</v>
       </c>
       <c r="AC73" s="16" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AD73" s="16" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AE73" s="16" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AF73" s="16" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="AG73" s="16" t="s">
-        <v>1856</v>
+        <v>1853</v>
       </c>
       <c r="AH73" s="16" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AI73" s="16" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AJ73" s="16" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
     </row>
-    <row r="74" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>73</v>
       </c>
@@ -14293,19 +14287,19 @@
         <v>1054</v>
       </c>
       <c r="O74" s="18" t="s">
+        <v>1581</v>
+      </c>
+      <c r="P74" s="18" t="s">
         <v>1582</v>
       </c>
-      <c r="P74" s="18" t="s">
+      <c r="Q74" s="18" t="s">
         <v>1583</v>
-      </c>
-      <c r="Q74" s="18" t="s">
-        <v>1584</v>
       </c>
       <c r="R74" s="18" t="s">
         <v>24</v>
       </c>
       <c r="S74" s="18" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="T74" s="18" t="s">
         <v>1122</v>
@@ -14317,37 +14311,37 @@
         <v>1008</v>
       </c>
       <c r="W74" s="18" t="s">
+        <v>1584</v>
+      </c>
+      <c r="X74" s="18" t="s">
         <v>1585</v>
-      </c>
-      <c r="X74" s="18" t="s">
-        <v>1586</v>
       </c>
       <c r="Y74" s="18" t="s">
         <v>1007</v>
       </c>
       <c r="Z74" s="18" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="AA74" s="18" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="AB74" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC74" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD74" s="18" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="AE74" s="18" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="AF74" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG74" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH74" s="18" t="s">
         <v>26</v>
@@ -14359,7 +14353,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="75" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>74</v>
       </c>
@@ -14394,28 +14388,28 @@
         <v>563</v>
       </c>
       <c r="L75" s="4" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="M75" s="4" t="s">
         <v>993</v>
       </c>
       <c r="N75" s="18" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="O75" s="18" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="P75" s="18" t="s">
+        <v>1587</v>
+      </c>
+      <c r="Q75" s="18" t="s">
         <v>1588</v>
-      </c>
-      <c r="Q75" s="18" t="s">
-        <v>1589</v>
       </c>
       <c r="R75" s="18" t="s">
         <v>24</v>
       </c>
       <c r="S75" s="18" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="T75" s="18" t="s">
         <v>1122</v>
@@ -14427,49 +14421,49 @@
         <v>1008</v>
       </c>
       <c r="W75" s="18" t="s">
+        <v>1589</v>
+      </c>
+      <c r="X75" s="18" t="s">
         <v>1590</v>
-      </c>
-      <c r="X75" s="18" t="s">
-        <v>1591</v>
       </c>
       <c r="Y75" s="18" t="s">
         <v>1007</v>
       </c>
       <c r="Z75" s="18" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="AA75" s="18" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AB75" s="18" t="s">
         <v>77</v>
       </c>
       <c r="AC75" s="18" t="s">
-        <v>1840</v>
+        <v>1838</v>
       </c>
       <c r="AD75" s="18" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="AE75" s="18" t="s">
         <v>1081</v>
       </c>
       <c r="AF75" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG75" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH75" s="19" t="s">
         <v>1216</v>
       </c>
       <c r="AI75" s="19" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="AJ75" s="18" t="s">
         <v>1151</v>
       </c>
     </row>
-    <row r="76" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>75</v>
       </c>
@@ -14510,19 +14504,19 @@
         <v>1054</v>
       </c>
       <c r="O76" s="18" t="s">
+        <v>1594</v>
+      </c>
+      <c r="P76" s="18" t="s">
         <v>1595</v>
       </c>
-      <c r="P76" s="18" t="s">
+      <c r="Q76" s="46" t="s">
         <v>1596</v>
-      </c>
-      <c r="Q76" s="46" t="s">
-        <v>1597</v>
       </c>
       <c r="R76" s="18" t="s">
         <v>24</v>
       </c>
       <c r="S76" s="18" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="T76" s="18" t="s">
         <v>1122</v>
@@ -14534,10 +14528,10 @@
         <v>1008</v>
       </c>
       <c r="W76" s="18" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="X76" s="18" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="Y76" s="18" t="s">
         <v>1007</v>
@@ -14546,25 +14540,25 @@
         <v>26</v>
       </c>
       <c r="AA76" s="18" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="AB76" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC76" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD76" s="18" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="AE76" s="18" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="AF76" s="18" t="s">
-        <v>1941</v>
+        <v>1938</v>
       </c>
       <c r="AG76" s="18" t="s">
-        <v>1853</v>
+        <v>1851</v>
       </c>
       <c r="AH76" s="18" t="s">
         <v>26</v>
@@ -14576,7 +14570,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="77" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>76</v>
       </c>
@@ -14617,19 +14611,19 @@
         <v>994</v>
       </c>
       <c r="O77" s="16" t="s">
+        <v>1599</v>
+      </c>
+      <c r="P77" s="16" t="s">
         <v>1600</v>
       </c>
-      <c r="P77" s="16" t="s">
+      <c r="Q77" s="45" t="s">
         <v>1601</v>
-      </c>
-      <c r="Q77" s="45" t="s">
-        <v>1602</v>
       </c>
       <c r="R77" s="16" t="s">
         <v>24</v>
       </c>
       <c r="S77" s="16" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="T77" s="16" t="s">
         <v>1122</v>
@@ -14641,37 +14635,37 @@
         <v>1008</v>
       </c>
       <c r="W77" s="16" t="s">
+        <v>1602</v>
+      </c>
+      <c r="X77" s="16" t="s">
         <v>1603</v>
-      </c>
-      <c r="X77" s="16" t="s">
-        <v>1604</v>
       </c>
       <c r="Y77" s="16" t="s">
         <v>1007</v>
       </c>
       <c r="Z77" s="16" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="AA77" s="16" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="AB77" s="16" t="s">
         <v>1126</v>
       </c>
       <c r="AC77" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD77" s="16" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="AE77" s="16" t="s">
         <v>1028</v>
       </c>
       <c r="AF77" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG77" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH77" s="16" t="s">
         <v>26</v>
@@ -14683,7 +14677,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="78" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>77</v>
       </c>
@@ -14724,37 +14718,37 @@
         <v>1011</v>
       </c>
       <c r="N78" s="16" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="O78" s="16" t="s">
+        <v>1606</v>
+      </c>
+      <c r="P78" s="16" t="s">
         <v>1607</v>
       </c>
-      <c r="P78" s="16" t="s">
+      <c r="Q78" s="45" t="s">
         <v>1608</v>
-      </c>
-      <c r="Q78" s="45" t="s">
-        <v>1609</v>
       </c>
       <c r="R78" s="16" t="s">
         <v>24</v>
       </c>
       <c r="S78" s="16" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="T78" s="16" t="s">
         <v>1122</v>
       </c>
       <c r="U78" s="16" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="V78" s="16" t="s">
         <v>1008</v>
       </c>
       <c r="W78" s="16" t="s">
+        <v>1610</v>
+      </c>
+      <c r="X78" s="16" t="s">
         <v>1611</v>
-      </c>
-      <c r="X78" s="16" t="s">
-        <v>1612</v>
       </c>
       <c r="Y78" s="16" t="s">
         <v>1007</v>
@@ -14763,25 +14757,25 @@
         <v>26</v>
       </c>
       <c r="AA78" s="16" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AB78" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC78" s="16" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="AD78" s="16" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="AE78" s="16" t="s">
         <v>997</v>
       </c>
       <c r="AF78" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG78" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH78" s="16" t="s">
         <v>26</v>
@@ -14793,7 +14787,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="79" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>78</v>
       </c>
@@ -14834,22 +14828,22 @@
         <v>1011</v>
       </c>
       <c r="N79" s="16" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="O79" s="16" t="s">
+        <v>1613</v>
+      </c>
+      <c r="P79" s="16" t="s">
         <v>1614</v>
       </c>
-      <c r="P79" s="16" t="s">
+      <c r="Q79" s="45" t="s">
         <v>1615</v>
-      </c>
-      <c r="Q79" s="45" t="s">
-        <v>1616</v>
       </c>
       <c r="R79" s="16" t="s">
         <v>24</v>
       </c>
       <c r="S79" s="16" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="T79" s="16" t="s">
         <v>1122</v>
@@ -14861,37 +14855,37 @@
         <v>1008</v>
       </c>
       <c r="W79" s="16" t="s">
+        <v>1616</v>
+      </c>
+      <c r="X79" s="16" t="s">
         <v>1617</v>
-      </c>
-      <c r="X79" s="16" t="s">
-        <v>1618</v>
       </c>
       <c r="Y79" s="16" t="s">
         <v>1007</v>
       </c>
       <c r="Z79" s="16" t="s">
+        <v>1618</v>
+      </c>
+      <c r="AA79" s="16" t="s">
+        <v>1842</v>
+      </c>
+      <c r="AB79" s="16" t="s">
         <v>1619</v>
       </c>
-      <c r="AA79" s="16" t="s">
-        <v>1844</v>
-      </c>
-      <c r="AB79" s="16" t="s">
+      <c r="AC79" s="16" t="s">
+        <v>1835</v>
+      </c>
+      <c r="AD79" s="16" t="s">
         <v>1620</v>
-      </c>
-      <c r="AC79" s="16" t="s">
-        <v>1837</v>
-      </c>
-      <c r="AD79" s="16" t="s">
-        <v>1621</v>
       </c>
       <c r="AE79" s="16" t="s">
         <v>1028</v>
       </c>
       <c r="AF79" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG79" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH79" s="16" t="s">
         <v>26</v>
@@ -14903,7 +14897,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="80" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>79</v>
       </c>
@@ -14941,22 +14935,22 @@
         <v>1011</v>
       </c>
       <c r="N80" s="16" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="O80" s="16" t="s">
+        <v>1621</v>
+      </c>
+      <c r="P80" s="16" t="s">
         <v>1622</v>
       </c>
-      <c r="P80" s="16" t="s">
+      <c r="Q80" s="45" t="s">
         <v>1623</v>
-      </c>
-      <c r="Q80" s="45" t="s">
-        <v>1624</v>
       </c>
       <c r="R80" s="16" t="s">
         <v>24</v>
       </c>
       <c r="S80" s="16" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="T80" s="16" t="s">
         <v>1122</v>
@@ -14968,25 +14962,25 @@
         <v>1008</v>
       </c>
       <c r="W80" s="16" t="s">
+        <v>1624</v>
+      </c>
+      <c r="X80" s="16" t="s">
         <v>1625</v>
-      </c>
-      <c r="X80" s="16" t="s">
-        <v>1626</v>
       </c>
       <c r="Y80" s="16" t="s">
         <v>1007</v>
       </c>
       <c r="Z80" s="16" t="s">
+        <v>1439</v>
+      </c>
+      <c r="AA80" s="16" t="s">
         <v>1440</v>
-      </c>
-      <c r="AA80" s="16" t="s">
-        <v>1441</v>
       </c>
       <c r="AB80" s="16" t="s">
         <v>1126</v>
       </c>
       <c r="AC80" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD80" s="16" t="s">
         <v>1239</v>
@@ -14995,10 +14989,10 @@
         <v>1028</v>
       </c>
       <c r="AF80" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG80" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH80" s="16" t="s">
         <v>26</v>
@@ -15010,7 +15004,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="81" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>80</v>
       </c>
@@ -15051,19 +15045,19 @@
         <v>1054</v>
       </c>
       <c r="O81" s="16" t="s">
+        <v>1626</v>
+      </c>
+      <c r="P81" s="16" t="s">
         <v>1627</v>
       </c>
-      <c r="P81" s="16" t="s">
+      <c r="Q81" s="45" t="s">
         <v>1628</v>
-      </c>
-      <c r="Q81" s="45" t="s">
-        <v>1629</v>
       </c>
       <c r="R81" s="16" t="s">
         <v>24</v>
       </c>
       <c r="S81" s="16" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="T81" s="16" t="s">
         <v>1122</v>
@@ -15075,37 +15069,37 @@
         <v>1008</v>
       </c>
       <c r="W81" s="16" t="s">
+        <v>1629</v>
+      </c>
+      <c r="X81" s="16" t="s">
         <v>1630</v>
-      </c>
-      <c r="X81" s="16" t="s">
-        <v>1631</v>
       </c>
       <c r="Y81" s="16" t="s">
         <v>1007</v>
       </c>
       <c r="Z81" s="16" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="AA81" s="16" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="AB81" s="16" t="s">
         <v>77</v>
       </c>
       <c r="AC81" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD81" s="16" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="AE81" s="16" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="AF81" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG81" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH81" s="16" t="s">
         <v>26</v>
@@ -15117,7 +15111,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="82" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>81</v>
       </c>
@@ -15152,7 +15146,7 @@
         <v>236</v>
       </c>
       <c r="L82" s="4" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="M82" s="4" t="s">
         <v>1011</v>
@@ -15161,19 +15155,19 @@
         <v>1054</v>
       </c>
       <c r="O82" s="18" t="s">
+        <v>1632</v>
+      </c>
+      <c r="P82" s="18" t="s">
         <v>1633</v>
       </c>
-      <c r="P82" s="18" t="s">
+      <c r="Q82" s="46" t="s">
         <v>1634</v>
-      </c>
-      <c r="Q82" s="46" t="s">
-        <v>1635</v>
       </c>
       <c r="R82" s="18" t="s">
         <v>24</v>
       </c>
       <c r="S82" s="18" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="T82" s="18" t="s">
         <v>1122</v>
@@ -15185,49 +15179,49 @@
         <v>1008</v>
       </c>
       <c r="W82" s="18" t="s">
+        <v>1635</v>
+      </c>
+      <c r="X82" s="18" t="s">
         <v>1636</v>
-      </c>
-      <c r="X82" s="18" t="s">
-        <v>1637</v>
       </c>
       <c r="Y82" s="18" t="s">
         <v>1007</v>
       </c>
       <c r="Z82" s="18" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="AA82" s="18" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="AB82" s="18" t="s">
         <v>1141</v>
       </c>
       <c r="AC82" s="18" t="s">
-        <v>1895</v>
+        <v>1892</v>
       </c>
       <c r="AD82" s="18" t="s">
-        <v>1905</v>
+        <v>1902</v>
       </c>
       <c r="AE82" s="18" t="s">
         <v>1081</v>
       </c>
       <c r="AF82" s="18" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="AG82" s="18" t="s">
-        <v>1862</v>
+        <v>1859</v>
       </c>
       <c r="AH82" s="34" t="s">
         <v>1216</v>
       </c>
       <c r="AI82" s="20" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="AJ82" s="18" t="s">
         <v>1151</v>
       </c>
     </row>
-    <row r="83" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>82</v>
       </c>
@@ -15262,7 +15256,7 @@
         <v>617</v>
       </c>
       <c r="L83" s="4" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="M83" s="4" t="s">
         <v>1011</v>
@@ -15271,19 +15265,19 @@
         <v>1054</v>
       </c>
       <c r="O83" s="18" t="s">
+        <v>1638</v>
+      </c>
+      <c r="P83" s="18" t="s">
         <v>1639</v>
       </c>
-      <c r="P83" s="18" t="s">
+      <c r="Q83" s="46" t="s">
         <v>1640</v>
-      </c>
-      <c r="Q83" s="46" t="s">
-        <v>1641</v>
       </c>
       <c r="R83" s="18" t="s">
         <v>24</v>
       </c>
       <c r="S83" s="18" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="T83" s="18" t="s">
         <v>1122</v>
@@ -15295,37 +15289,37 @@
         <v>1008</v>
       </c>
       <c r="W83" s="18" t="s">
+        <v>1641</v>
+      </c>
+      <c r="X83" s="18" t="s">
         <v>1642</v>
-      </c>
-      <c r="X83" s="18" t="s">
-        <v>1643</v>
       </c>
       <c r="Y83" s="18" t="s">
         <v>1007</v>
       </c>
       <c r="Z83" s="18" t="s">
+        <v>1643</v>
+      </c>
+      <c r="AA83" s="18" t="s">
+        <v>1842</v>
+      </c>
+      <c r="AB83" s="18" t="s">
+        <v>1848</v>
+      </c>
+      <c r="AC83" s="18" t="s">
+        <v>1893</v>
+      </c>
+      <c r="AD83" s="18" t="s">
         <v>1644</v>
-      </c>
-      <c r="AA83" s="18" t="s">
-        <v>1844</v>
-      </c>
-      <c r="AB83" s="18" t="s">
-        <v>1850</v>
-      </c>
-      <c r="AC83" s="18" t="s">
-        <v>1896</v>
-      </c>
-      <c r="AD83" s="18" t="s">
-        <v>1645</v>
       </c>
       <c r="AE83" s="18" t="s">
         <v>1081</v>
       </c>
       <c r="AF83" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG83" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH83" s="18" t="s">
         <v>26</v>
@@ -15337,7 +15331,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="84" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>83</v>
       </c>
@@ -15381,34 +15375,34 @@
         <v>1054</v>
       </c>
       <c r="O84" s="18" t="s">
+        <v>1645</v>
+      </c>
+      <c r="P84" s="18" t="s">
         <v>1646</v>
       </c>
-      <c r="P84" s="18" t="s">
+      <c r="Q84" s="46" t="s">
         <v>1647</v>
-      </c>
-      <c r="Q84" s="46" t="s">
-        <v>1648</v>
       </c>
       <c r="R84" s="18" t="s">
         <v>24</v>
       </c>
       <c r="S84" s="18" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="T84" s="18" t="s">
         <v>1122</v>
       </c>
       <c r="U84" s="18" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="V84" s="18" t="s">
         <v>1008</v>
       </c>
       <c r="W84" s="18" t="s">
+        <v>1649</v>
+      </c>
+      <c r="X84" s="18" t="s">
         <v>1650</v>
-      </c>
-      <c r="X84" s="18" t="s">
-        <v>1651</v>
       </c>
       <c r="Y84" s="18" t="s">
         <v>1007</v>
@@ -15417,25 +15411,25 @@
         <v>26</v>
       </c>
       <c r="AA84" s="18" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AB84" s="18" t="s">
         <v>1281</v>
       </c>
       <c r="AC84" s="18" t="s">
-        <v>1897</v>
+        <v>1894</v>
       </c>
       <c r="AD84" s="18" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="AE84" s="18" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="AF84" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG84" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH84" s="18" t="s">
         <v>26</v>
@@ -15447,7 +15441,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="85" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>84</v>
       </c>
@@ -15491,19 +15485,19 @@
         <v>995</v>
       </c>
       <c r="O85" s="18" t="s">
+        <v>1651</v>
+      </c>
+      <c r="P85" s="18" t="s">
         <v>1652</v>
       </c>
-      <c r="P85" s="18" t="s">
+      <c r="Q85" s="18" t="s">
         <v>1653</v>
-      </c>
-      <c r="Q85" s="18" t="s">
-        <v>1654</v>
       </c>
       <c r="R85" s="18" t="s">
         <v>24</v>
       </c>
       <c r="S85" s="18" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="T85" s="18" t="s">
         <v>1122</v>
@@ -15512,44 +15506,44 @@
         <v>1146</v>
       </c>
       <c r="V85" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="W85" s="18"/>
       <c r="X85" s="18"/>
       <c r="Y85" s="18"/>
       <c r="Z85" s="18"/>
       <c r="AA85" s="18" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="AB85" s="18" t="s">
         <v>54</v>
       </c>
       <c r="AC85" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AD85" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AE85" s="18" t="s">
         <v>1259</v>
       </c>
       <c r="AF85" s="18" t="s">
-        <v>1941</v>
+        <v>1938</v>
       </c>
       <c r="AG85" s="18" t="s">
-        <v>1950</v>
+        <v>1947</v>
       </c>
       <c r="AH85" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AI85" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AJ85" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
     </row>
-    <row r="86" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>85</v>
       </c>
@@ -15584,7 +15578,7 @@
         <v>639</v>
       </c>
       <c r="L86" s="4" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="M86" s="4" t="s">
         <v>1011</v>
@@ -15593,19 +15587,19 @@
         <v>1054</v>
       </c>
       <c r="O86" s="18" t="s">
+        <v>1654</v>
+      </c>
+      <c r="P86" s="18" t="s">
         <v>1655</v>
       </c>
-      <c r="P86" s="18" t="s">
+      <c r="Q86" s="46" t="s">
         <v>1656</v>
-      </c>
-      <c r="Q86" s="46" t="s">
-        <v>1657</v>
       </c>
       <c r="R86" s="18" t="s">
         <v>24</v>
       </c>
       <c r="S86" s="18" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="T86" s="18" t="s">
         <v>1122</v>
@@ -15614,13 +15608,13 @@
         <v>1146</v>
       </c>
       <c r="V86" s="18" t="s">
+        <v>1658</v>
+      </c>
+      <c r="W86" s="18" t="s">
         <v>1659</v>
       </c>
-      <c r="W86" s="18" t="s">
+      <c r="X86" s="18" t="s">
         <v>1660</v>
-      </c>
-      <c r="X86" s="18" t="s">
-        <v>1661</v>
       </c>
       <c r="Y86" s="18" t="s">
         <v>1007</v>
@@ -15629,25 +15623,25 @@
         <v>26</v>
       </c>
       <c r="AA86" s="18" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="AB86" s="18" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="AC86" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD86" s="18" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="AE86" s="18" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="AF86" s="18" t="s">
         <v>25</v>
       </c>
       <c r="AG86" s="18" t="s">
-        <v>1935</v>
+        <v>1932</v>
       </c>
       <c r="AH86" s="18" t="s">
         <v>26</v>
@@ -15659,7 +15653,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="87" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>86</v>
       </c>
@@ -15694,7 +15688,7 @@
         <v>647</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="M87" s="2" t="s">
         <v>993</v>
@@ -15703,19 +15697,19 @@
         <v>994</v>
       </c>
       <c r="O87" s="16" t="s">
+        <v>1662</v>
+      </c>
+      <c r="P87" s="16" t="s">
         <v>1663</v>
       </c>
-      <c r="P87" s="16" t="s">
+      <c r="Q87" s="16" t="s">
         <v>1664</v>
-      </c>
-      <c r="Q87" s="16" t="s">
-        <v>1665</v>
       </c>
       <c r="R87" s="16" t="s">
         <v>24</v>
       </c>
       <c r="S87" s="16" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="T87" s="16" t="s">
         <v>1122</v>
@@ -15724,13 +15718,13 @@
         <v>1146</v>
       </c>
       <c r="V87" s="16" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="W87" s="16" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="X87" s="16" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Y87" s="16" t="s">
         <v>1007</v>
@@ -15739,37 +15733,37 @@
         <v>26</v>
       </c>
       <c r="AA87" s="16" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="AB87" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC87" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD87" s="16" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="AE87" s="16" t="s">
-        <v>1883</v>
+        <v>1880</v>
       </c>
       <c r="AF87" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG87" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH87" s="22" t="s">
         <v>1216</v>
       </c>
       <c r="AI87" s="22" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="AJ87" s="16" t="s">
         <v>1151</v>
       </c>
     </row>
-    <row r="88" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>87</v>
       </c>
@@ -15804,28 +15798,28 @@
         <v>268</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="M88" s="2" t="s">
         <v>993</v>
       </c>
       <c r="N88" s="16" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="O88" s="16" t="s">
+        <v>1668</v>
+      </c>
+      <c r="P88" s="16" t="s">
         <v>1669</v>
       </c>
-      <c r="P88" s="16" t="s">
+      <c r="Q88" s="16" t="s">
         <v>1670</v>
-      </c>
-      <c r="Q88" s="16" t="s">
-        <v>1671</v>
       </c>
       <c r="R88" s="16" t="s">
         <v>24</v>
       </c>
       <c r="S88" s="16" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="T88" s="16" t="s">
         <v>1122</v>
@@ -15837,49 +15831,49 @@
         <v>1008</v>
       </c>
       <c r="W88" s="16" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="X88" s="16" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="Y88" s="16" t="s">
         <v>1007</v>
       </c>
       <c r="Z88" s="16" t="s">
+        <v>1672</v>
+      </c>
+      <c r="AA88" s="16" t="s">
+        <v>1842</v>
+      </c>
+      <c r="AB88" s="16" t="s">
         <v>1673</v>
       </c>
-      <c r="AA88" s="16" t="s">
-        <v>1844</v>
-      </c>
-      <c r="AB88" s="16" t="s">
+      <c r="AC88" s="16" t="s">
+        <v>1920</v>
+      </c>
+      <c r="AD88" s="16" t="s">
         <v>1674</v>
-      </c>
-      <c r="AC88" s="16" t="s">
-        <v>1923</v>
-      </c>
-      <c r="AD88" s="16" t="s">
-        <v>1675</v>
       </c>
       <c r="AE88" s="21" t="s">
         <v>997</v>
       </c>
       <c r="AF88" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG88" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH88" s="22" t="s">
         <v>1216</v>
       </c>
       <c r="AI88" s="22" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="AJ88" s="16" t="s">
         <v>1151</v>
       </c>
     </row>
-    <row r="89" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>88</v>
       </c>
@@ -15920,19 +15914,19 @@
         <v>1054</v>
       </c>
       <c r="O89" s="16" t="s">
+        <v>1676</v>
+      </c>
+      <c r="P89" s="16" t="s">
+        <v>1352</v>
+      </c>
+      <c r="Q89" s="45" t="s">
         <v>1677</v>
-      </c>
-      <c r="P89" s="16" t="s">
-        <v>1353</v>
-      </c>
-      <c r="Q89" s="45" t="s">
-        <v>1678</v>
       </c>
       <c r="R89" s="16" t="s">
         <v>24</v>
       </c>
       <c r="S89" s="16" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="T89" s="16" t="s">
         <v>1122</v>
@@ -15944,37 +15938,37 @@
         <v>1008</v>
       </c>
       <c r="W89" s="16" t="s">
+        <v>1678</v>
+      </c>
+      <c r="X89" s="16" t="s">
         <v>1679</v>
-      </c>
-      <c r="X89" s="16" t="s">
-        <v>1680</v>
       </c>
       <c r="Y89" s="16" t="s">
         <v>1007</v>
       </c>
       <c r="Z89" s="16" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="AA89" s="16" t="s">
         <v>990</v>
       </c>
       <c r="AB89" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC89" s="16" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="AD89" s="21" t="s">
         <v>1245</v>
       </c>
       <c r="AE89" s="16" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="AF89" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG89" s="16" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH89" s="16" t="s">
         <v>26</v>
@@ -15986,7 +15980,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="90" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>89</v>
       </c>
@@ -16021,7 +16015,7 @@
         <v>109</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="M90" s="2" t="s">
         <v>993</v>
@@ -16030,19 +16024,19 @@
         <v>995</v>
       </c>
       <c r="O90" s="16" t="s">
+        <v>1682</v>
+      </c>
+      <c r="P90" s="16" t="s">
         <v>1683</v>
       </c>
-      <c r="P90" s="16" t="s">
+      <c r="Q90" s="16" t="s">
         <v>1684</v>
-      </c>
-      <c r="Q90" s="16" t="s">
-        <v>1685</v>
       </c>
       <c r="R90" s="16" t="s">
         <v>24</v>
       </c>
       <c r="S90" s="16" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="T90" s="16" t="s">
         <v>1122</v>
@@ -16063,40 +16057,40 @@
         <v>1007</v>
       </c>
       <c r="Z90" s="16" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="AA90" s="16" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="AB90" s="16" t="s">
         <v>1086</v>
       </c>
       <c r="AC90" s="16" t="s">
-        <v>1931</v>
+        <v>1928</v>
       </c>
       <c r="AD90" s="16" t="s">
-        <v>1903</v>
+        <v>1900</v>
       </c>
       <c r="AE90" s="16" t="s">
         <v>997</v>
       </c>
       <c r="AF90" s="16" t="s">
-        <v>1858</v>
+        <v>1855</v>
       </c>
       <c r="AG90" s="16" t="s">
-        <v>1957</v>
+        <v>1954</v>
       </c>
       <c r="AH90" s="22" t="s">
         <v>1216</v>
       </c>
       <c r="AI90" s="22" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="AJ90" s="16" t="s">
         <v>1151</v>
       </c>
     </row>
-    <row r="91" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>90</v>
       </c>
@@ -16137,22 +16131,22 @@
         <v>1011</v>
       </c>
       <c r="N91" s="16" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="O91" s="16" t="s">
+        <v>1687</v>
+      </c>
+      <c r="P91" s="16" t="s">
         <v>1688</v>
       </c>
-      <c r="P91" s="16" t="s">
+      <c r="Q91" s="45" t="s">
         <v>1689</v>
-      </c>
-      <c r="Q91" s="45" t="s">
-        <v>1690</v>
       </c>
       <c r="R91" s="16" t="s">
         <v>24</v>
       </c>
       <c r="S91" s="16" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="T91" s="16" t="s">
         <v>1122</v>
@@ -16164,10 +16158,10 @@
         <v>1008</v>
       </c>
       <c r="W91" s="16" t="s">
+        <v>1690</v>
+      </c>
+      <c r="X91" s="16" t="s">
         <v>1691</v>
-      </c>
-      <c r="X91" s="16" t="s">
-        <v>1692</v>
       </c>
       <c r="Y91" s="16" t="s">
         <v>1007</v>
@@ -16176,16 +16170,16 @@
         <v>26</v>
       </c>
       <c r="AA91" s="16" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="AB91" s="16" t="s">
         <v>77</v>
       </c>
       <c r="AC91" s="16" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="AD91" s="16" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="AE91" s="16" t="s">
         <v>1028</v>
@@ -16194,19 +16188,19 @@
         <v>237</v>
       </c>
       <c r="AG91" s="16" t="s">
-        <v>1865</v>
+        <v>1862</v>
       </c>
       <c r="AH91" s="22" t="s">
         <v>1216</v>
       </c>
       <c r="AI91" s="22" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="AJ91" s="16" t="s">
         <v>1151</v>
       </c>
     </row>
-    <row r="92" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>91</v>
       </c>
@@ -16247,22 +16241,22 @@
         <v>993</v>
       </c>
       <c r="N92" s="18" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="O92" s="18" t="s">
+        <v>1694</v>
+      </c>
+      <c r="P92" s="18" t="s">
         <v>1695</v>
       </c>
-      <c r="P92" s="18" t="s">
+      <c r="Q92" s="18" t="s">
         <v>1696</v>
-      </c>
-      <c r="Q92" s="18" t="s">
-        <v>1697</v>
       </c>
       <c r="R92" s="18" t="s">
         <v>24</v>
       </c>
       <c r="S92" s="18" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="T92" s="18" t="s">
         <v>1122</v>
@@ -16274,37 +16268,37 @@
         <v>1008</v>
       </c>
       <c r="W92" s="18" t="s">
+        <v>1697</v>
+      </c>
+      <c r="X92" s="18" t="s">
         <v>1698</v>
-      </c>
-      <c r="X92" s="18" t="s">
-        <v>1699</v>
       </c>
       <c r="Y92" s="18" t="s">
         <v>1007</v>
       </c>
       <c r="Z92" s="18" t="s">
+        <v>1699</v>
+      </c>
+      <c r="AA92" s="18" t="s">
+        <v>1845</v>
+      </c>
+      <c r="AB92" s="18" t="s">
         <v>1700</v>
       </c>
-      <c r="AA92" s="18" t="s">
-        <v>1847</v>
-      </c>
-      <c r="AB92" s="18" t="s">
+      <c r="AC92" s="18" t="s">
         <v>1701</v>
       </c>
-      <c r="AC92" s="18" t="s">
+      <c r="AD92" s="18" t="s">
         <v>1702</v>
       </c>
-      <c r="AD92" s="18" t="s">
+      <c r="AE92" s="18" t="s">
         <v>1703</v>
       </c>
-      <c r="AE92" s="18" t="s">
-        <v>1704</v>
-      </c>
       <c r="AF92" s="18" t="s">
-        <v>1857</v>
+        <v>1854</v>
       </c>
       <c r="AG92" s="18" t="s">
-        <v>1958</v>
+        <v>1955</v>
       </c>
       <c r="AH92" s="18" t="s">
         <v>26</v>
@@ -16316,7 +16310,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="93" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>92</v>
       </c>
@@ -16348,7 +16342,7 @@
         <v>690</v>
       </c>
       <c r="L93" s="4" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="M93" s="4" t="s">
         <v>993</v>
@@ -16357,19 +16351,19 @@
         <v>994</v>
       </c>
       <c r="O93" s="18" t="s">
+        <v>1704</v>
+      </c>
+      <c r="P93" s="18" t="s">
         <v>1705</v>
       </c>
-      <c r="P93" s="18" t="s">
+      <c r="Q93" s="18" t="s">
         <v>1706</v>
-      </c>
-      <c r="Q93" s="18" t="s">
-        <v>1707</v>
       </c>
       <c r="R93" s="18" t="s">
         <v>24</v>
       </c>
       <c r="S93" s="18" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="T93" s="18" t="s">
         <v>1122</v>
@@ -16381,10 +16375,10 @@
         <v>1008</v>
       </c>
       <c r="W93" s="18" t="s">
+        <v>1707</v>
+      </c>
+      <c r="X93" s="18" t="s">
         <v>1708</v>
-      </c>
-      <c r="X93" s="18" t="s">
-        <v>1709</v>
       </c>
       <c r="Y93" s="18" t="s">
         <v>1007</v>
@@ -16393,16 +16387,16 @@
         <v>26</v>
       </c>
       <c r="AA93" s="18" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="AB93" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC93" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD93" s="18" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="AE93" s="18" t="s">
         <v>1259</v>
@@ -16411,7 +16405,7 @@
         <v>25</v>
       </c>
       <c r="AG93" s="18" t="s">
-        <v>1955</v>
+        <v>1952</v>
       </c>
       <c r="AH93" s="18" t="s">
         <v>26</v>
@@ -16423,7 +16417,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="94" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>93</v>
       </c>
@@ -16461,22 +16455,22 @@
         <v>1011</v>
       </c>
       <c r="N94" s="18" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="O94" s="18" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="P94" s="18" t="s">
         <v>1242</v>
       </c>
       <c r="Q94" s="46" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="R94" s="18" t="s">
         <v>24</v>
       </c>
       <c r="S94" s="18" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="T94" s="18" t="s">
         <v>1122</v>
@@ -16488,37 +16482,37 @@
         <v>1008</v>
       </c>
       <c r="W94" s="18" t="s">
+        <v>1712</v>
+      </c>
+      <c r="X94" s="18" t="s">
         <v>1713</v>
-      </c>
-      <c r="X94" s="18" t="s">
-        <v>1714</v>
       </c>
       <c r="Y94" s="18" t="s">
         <v>1007</v>
       </c>
       <c r="Z94" s="18" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="AA94" s="18" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="AB94" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC94" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD94" s="18" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="AE94" s="18" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="AF94" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG94" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH94" s="18" t="s">
         <v>26</v>
@@ -16530,7 +16524,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="95" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>94</v>
       </c>
@@ -16571,76 +16565,76 @@
         <v>1011</v>
       </c>
       <c r="N95" s="18" t="s">
+        <v>1715</v>
+      </c>
+      <c r="O95" s="18" t="s">
         <v>1716</v>
       </c>
-      <c r="O95" s="18" t="s">
+      <c r="P95" s="18" t="s">
         <v>1717</v>
       </c>
-      <c r="P95" s="18" t="s">
+      <c r="Q95" s="46" t="s">
         <v>1718</v>
-      </c>
-      <c r="Q95" s="46" t="s">
-        <v>1719</v>
       </c>
       <c r="R95" s="18" t="s">
         <v>24</v>
       </c>
       <c r="S95" s="18" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="T95" s="18" t="s">
         <v>1122</v>
       </c>
       <c r="U95" s="18" t="s">
+        <v>1719</v>
+      </c>
+      <c r="V95" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="W95" s="18" t="s">
         <v>1720</v>
       </c>
-      <c r="V95" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="W95" s="18" t="s">
+      <c r="X95" s="18" t="s">
         <v>1721</v>
-      </c>
-      <c r="X95" s="18" t="s">
-        <v>1722</v>
       </c>
       <c r="Y95" s="18" t="s">
         <v>1007</v>
       </c>
       <c r="Z95" s="18" t="s">
+        <v>1722</v>
+      </c>
+      <c r="AA95" s="18" t="s">
+        <v>1842</v>
+      </c>
+      <c r="AB95" s="18" t="s">
         <v>1723</v>
       </c>
-      <c r="AA95" s="18" t="s">
-        <v>1844</v>
-      </c>
-      <c r="AB95" s="18" t="s">
-        <v>1724</v>
-      </c>
       <c r="AC95" s="18" t="s">
-        <v>1838</v>
+        <v>1836</v>
       </c>
       <c r="AD95" s="18" t="s">
-        <v>1907</v>
+        <v>1904</v>
       </c>
       <c r="AE95" s="18" t="s">
         <v>1028</v>
       </c>
       <c r="AF95" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG95" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH95" s="19" t="s">
         <v>1216</v>
       </c>
       <c r="AI95" s="19" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="AJ95" s="18" t="s">
         <v>1151</v>
       </c>
     </row>
-    <row r="96" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>95</v>
       </c>
@@ -16681,19 +16675,19 @@
         <v>994</v>
       </c>
       <c r="O96" s="18" t="s">
+        <v>1725</v>
+      </c>
+      <c r="P96" s="18" t="s">
         <v>1726</v>
       </c>
-      <c r="P96" s="18" t="s">
+      <c r="Q96" s="46" t="s">
         <v>1727</v>
-      </c>
-      <c r="Q96" s="46" t="s">
-        <v>1728</v>
       </c>
       <c r="R96" s="18" t="s">
         <v>24</v>
       </c>
       <c r="S96" s="18" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="T96" s="18" t="s">
         <v>1122</v>
@@ -16705,37 +16699,37 @@
         <v>1008</v>
       </c>
       <c r="W96" s="18" t="s">
+        <v>1728</v>
+      </c>
+      <c r="X96" s="18" t="s">
         <v>1729</v>
-      </c>
-      <c r="X96" s="18" t="s">
-        <v>1730</v>
       </c>
       <c r="Y96" s="18" t="s">
         <v>1007</v>
       </c>
       <c r="Z96" s="18" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="AA96" s="18" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="AB96" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC96" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD96" s="18" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="AE96" s="18" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="AF96" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG96" s="18" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH96" s="18" t="s">
         <v>26</v>
@@ -16747,7 +16741,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="97" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>96</v>
       </c>
@@ -16791,65 +16785,65 @@
         <v>995</v>
       </c>
       <c r="O97" s="13" t="s">
+        <v>1733</v>
+      </c>
+      <c r="P97" s="13" t="s">
         <v>1734</v>
       </c>
-      <c r="P97" s="13" t="s">
+      <c r="Q97" s="13" t="s">
         <v>1735</v>
-      </c>
-      <c r="Q97" s="13" t="s">
-        <v>1736</v>
       </c>
       <c r="R97" s="13" t="s">
         <v>24</v>
       </c>
       <c r="S97" s="13" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="T97" s="13" t="s">
         <v>1122</v>
       </c>
       <c r="U97" s="13" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="V97" s="13" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="W97" s="13"/>
       <c r="X97" s="13"/>
       <c r="Y97" s="13"/>
       <c r="Z97" s="13"/>
       <c r="AA97" s="13" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AB97" s="13" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AC97" s="13" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AD97" s="13" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AE97" s="13" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AF97" s="13" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AG97" s="13" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AH97" s="13" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AI97" s="13" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AJ97" s="2" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
     </row>
-    <row r="98" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>97</v>
       </c>
@@ -16884,43 +16878,43 @@
         <v>725</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="M98" s="2" t="s">
         <v>993</v>
       </c>
       <c r="N98" s="13" t="s">
+        <v>1737</v>
+      </c>
+      <c r="O98" s="13" t="s">
         <v>1738</v>
       </c>
-      <c r="O98" s="13" t="s">
+      <c r="P98" s="13" t="s">
         <v>1739</v>
       </c>
-      <c r="P98" s="13" t="s">
+      <c r="Q98" s="13" t="s">
         <v>1740</v>
-      </c>
-      <c r="Q98" s="13" t="s">
-        <v>1741</v>
       </c>
       <c r="R98" s="13" t="s">
         <v>24</v>
       </c>
       <c r="S98" s="13" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="T98" s="13" t="s">
         <v>1122</v>
       </c>
       <c r="U98" s="13" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="V98" s="13" t="s">
         <v>1008</v>
       </c>
       <c r="W98" s="13" t="s">
+        <v>1742</v>
+      </c>
+      <c r="X98" s="13" t="s">
         <v>1743</v>
-      </c>
-      <c r="X98" s="13" t="s">
-        <v>1744</v>
       </c>
       <c r="Y98" s="13" t="s">
         <v>1007</v>
@@ -16929,25 +16923,25 @@
         <v>26</v>
       </c>
       <c r="AA98" s="13" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="AB98" s="13" t="s">
         <v>77</v>
       </c>
       <c r="AC98" s="13" t="s">
-        <v>1928</v>
+        <v>1925</v>
       </c>
       <c r="AD98" s="13" t="s">
+        <v>1744</v>
+      </c>
+      <c r="AE98" s="13" t="s">
         <v>1745</v>
       </c>
-      <c r="AE98" s="13" t="s">
-        <v>1746</v>
-      </c>
       <c r="AF98" s="13" t="s">
-        <v>1937</v>
+        <v>1934</v>
       </c>
       <c r="AG98" s="13" t="s">
-        <v>1859</v>
+        <v>1856</v>
       </c>
       <c r="AH98" s="13" t="s">
         <v>1064</v>
@@ -16959,7 +16953,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="99" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>98</v>
       </c>
@@ -16994,7 +16988,7 @@
         <v>268</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="M99" s="2" t="s">
         <v>993</v>
@@ -17003,19 +16997,19 @@
         <v>981</v>
       </c>
       <c r="O99" s="13" t="s">
+        <v>1746</v>
+      </c>
+      <c r="P99" s="13" t="s">
         <v>1747</v>
       </c>
-      <c r="P99" s="13" t="s">
+      <c r="Q99" s="13" t="s">
         <v>1748</v>
-      </c>
-      <c r="Q99" s="13" t="s">
-        <v>1749</v>
       </c>
       <c r="R99" s="13" t="s">
         <v>24</v>
       </c>
       <c r="S99" s="13" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="T99" s="13" t="s">
         <v>1122</v>
@@ -17027,49 +17021,49 @@
         <v>1008</v>
       </c>
       <c r="W99" s="13" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="X99" s="13" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="Y99" s="13" t="s">
         <v>1007</v>
       </c>
       <c r="Z99" s="13" t="s">
+        <v>1749</v>
+      </c>
+      <c r="AA99" s="13" t="s">
+        <v>1842</v>
+      </c>
+      <c r="AB99" s="13" t="s">
         <v>1750</v>
       </c>
-      <c r="AA99" s="13" t="s">
-        <v>1844</v>
-      </c>
-      <c r="AB99" s="13" t="s">
-        <v>1751</v>
-      </c>
       <c r="AC99" s="13" t="s">
-        <v>1898</v>
+        <v>1895</v>
       </c>
       <c r="AD99" s="13" t="s">
-        <v>1904</v>
+        <v>1901</v>
       </c>
       <c r="AE99" s="13" t="s">
-        <v>1966</v>
+        <v>1963</v>
       </c>
       <c r="AF99" s="13" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG99" s="13" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH99" s="15" t="s">
         <v>1216</v>
       </c>
       <c r="AI99" s="15" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="AJ99" s="13" t="s">
         <v>1151</v>
       </c>
     </row>
-    <row r="100" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>99</v>
       </c>
@@ -17104,7 +17098,7 @@
         <v>549</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="M100" s="2" t="s">
         <v>993</v>
@@ -17113,61 +17107,61 @@
         <v>994</v>
       </c>
       <c r="O100" s="13" t="s">
+        <v>1752</v>
+      </c>
+      <c r="P100" s="13" t="s">
         <v>1753</v>
       </c>
-      <c r="P100" s="13" t="s">
+      <c r="Q100" s="13" t="s">
         <v>1754</v>
-      </c>
-      <c r="Q100" s="13" t="s">
-        <v>1755</v>
       </c>
       <c r="R100" s="13" t="s">
         <v>24</v>
       </c>
       <c r="S100" s="13" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="T100" s="13" t="s">
         <v>1122</v>
       </c>
       <c r="U100" s="13" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="V100" s="13" t="s">
         <v>1008</v>
       </c>
       <c r="W100" s="13" t="s">
+        <v>1756</v>
+      </c>
+      <c r="X100" s="13" t="s">
         <v>1757</v>
       </c>
-      <c r="X100" s="13" t="s">
+      <c r="Y100" s="13" t="s">
         <v>1758</v>
       </c>
-      <c r="Y100" s="13" t="s">
+      <c r="Z100" s="13" t="s">
         <v>1759</v>
       </c>
-      <c r="Z100" s="13" t="s">
+      <c r="AA100" s="13" t="s">
+        <v>1842</v>
+      </c>
+      <c r="AB100" s="13" t="s">
         <v>1760</v>
       </c>
-      <c r="AA100" s="13" t="s">
-        <v>1844</v>
-      </c>
-      <c r="AB100" s="13" t="s">
+      <c r="AC100" s="13" t="s">
+        <v>1930</v>
+      </c>
+      <c r="AD100" s="13" t="s">
         <v>1761</v>
-      </c>
-      <c r="AC100" s="13" t="s">
-        <v>1933</v>
-      </c>
-      <c r="AD100" s="13" t="s">
-        <v>1762</v>
       </c>
       <c r="AE100" s="13" t="s">
         <v>1028</v>
       </c>
       <c r="AF100" s="13" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG100" s="13" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH100" s="13" t="s">
         <v>26</v>
@@ -17179,7 +17173,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="101" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>100</v>
       </c>
@@ -17223,19 +17217,19 @@
         <v>1054</v>
       </c>
       <c r="O101" s="13" t="s">
+        <v>1762</v>
+      </c>
+      <c r="P101" s="13" t="s">
         <v>1763</v>
       </c>
-      <c r="P101" s="13" t="s">
+      <c r="Q101" s="44" t="s">
         <v>1764</v>
-      </c>
-      <c r="Q101" s="44" t="s">
-        <v>1765</v>
       </c>
       <c r="R101" s="13" t="s">
         <v>24</v>
       </c>
       <c r="S101" s="13" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="T101" s="13" t="s">
         <v>1122</v>
@@ -17247,37 +17241,37 @@
         <v>1008</v>
       </c>
       <c r="W101" s="13" t="s">
+        <v>1765</v>
+      </c>
+      <c r="X101" s="13" t="s">
         <v>1766</v>
-      </c>
-      <c r="X101" s="13" t="s">
-        <v>1767</v>
       </c>
       <c r="Y101" s="13" t="s">
         <v>1007</v>
       </c>
       <c r="Z101" s="13" t="s">
+        <v>1767</v>
+      </c>
+      <c r="AA101" s="13" t="s">
+        <v>1842</v>
+      </c>
+      <c r="AB101" s="13" t="s">
+        <v>1848</v>
+      </c>
+      <c r="AC101" s="13" t="s">
+        <v>1554</v>
+      </c>
+      <c r="AD101" s="13" t="s">
         <v>1768</v>
       </c>
-      <c r="AA101" s="13" t="s">
-        <v>1844</v>
-      </c>
-      <c r="AB101" s="13" t="s">
-        <v>1850</v>
-      </c>
-      <c r="AC101" s="13" t="s">
-        <v>1555</v>
-      </c>
-      <c r="AD101" s="13" t="s">
-        <v>1769</v>
-      </c>
       <c r="AE101" s="13" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="AF101" s="13" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG101" s="13" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH101" s="13" t="s">
         <v>26</v>
@@ -17289,7 +17283,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="102" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>101</v>
       </c>
@@ -17330,61 +17324,61 @@
         <v>995</v>
       </c>
       <c r="O102" s="11" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="P102" s="11" t="s">
         <v>1204</v>
       </c>
       <c r="Q102" s="43" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="R102" s="11" t="s">
         <v>24</v>
       </c>
       <c r="S102" s="11" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="T102" s="11" t="s">
+        <v>1771</v>
+      </c>
+      <c r="U102" s="11" t="s">
         <v>1772</v>
-      </c>
-      <c r="U102" s="11" t="s">
-        <v>1773</v>
       </c>
       <c r="V102" s="11" t="s">
         <v>1008</v>
       </c>
       <c r="W102" s="11" t="s">
+        <v>1773</v>
+      </c>
+      <c r="X102" s="11" t="s">
         <v>1774</v>
-      </c>
-      <c r="X102" s="11" t="s">
-        <v>1775</v>
       </c>
       <c r="Y102" s="11" t="s">
         <v>1007</v>
       </c>
       <c r="Z102" s="11" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="AA102" s="11" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="AB102" s="11" t="s">
         <v>1212</v>
       </c>
       <c r="AC102" s="11" t="s">
-        <v>1839</v>
+        <v>1837</v>
       </c>
       <c r="AD102" s="11" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="AE102" s="11" t="s">
         <v>997</v>
       </c>
       <c r="AF102" s="11" t="s">
-        <v>1948</v>
+        <v>1945</v>
       </c>
       <c r="AG102" s="11" t="s">
-        <v>1956</v>
+        <v>1953</v>
       </c>
       <c r="AH102" s="11" t="s">
         <v>26</v>
@@ -17396,7 +17390,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="103" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>102</v>
       </c>
@@ -17440,34 +17434,34 @@
         <v>994</v>
       </c>
       <c r="O103" s="11" t="s">
+        <v>1777</v>
+      </c>
+      <c r="P103" s="11" t="s">
+        <v>1964</v>
+      </c>
+      <c r="Q103" s="43" t="s">
         <v>1778</v>
-      </c>
-      <c r="P103" s="11" t="s">
-        <v>1779</v>
-      </c>
-      <c r="Q103" s="43" t="s">
-        <v>1780</v>
       </c>
       <c r="R103" s="11" t="s">
         <v>24</v>
       </c>
       <c r="S103" s="11" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="T103" s="11" t="s">
         <v>1122</v>
       </c>
       <c r="U103" s="11" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="V103" s="11" t="s">
         <v>1008</v>
       </c>
       <c r="W103" s="11" t="s">
-        <v>1781</v>
+        <v>1779</v>
       </c>
       <c r="X103" s="11" t="s">
-        <v>1782</v>
+        <v>1780</v>
       </c>
       <c r="Y103" s="11" t="s">
         <v>1007</v>
@@ -17476,25 +17470,25 @@
         <v>26</v>
       </c>
       <c r="AA103" s="11" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AB103" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC103" s="11" t="s">
-        <v>1783</v>
+        <v>1781</v>
       </c>
       <c r="AD103" s="11" t="s">
-        <v>1784</v>
+        <v>1782</v>
       </c>
       <c r="AE103" s="11" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="AF103" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG103" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH103" s="11" t="s">
         <v>26</v>
@@ -17506,7 +17500,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="104" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>103</v>
       </c>
@@ -17550,19 +17544,19 @@
         <v>981</v>
       </c>
       <c r="O104" s="11" t="s">
+        <v>1783</v>
+      </c>
+      <c r="P104" s="11" t="s">
+        <v>1784</v>
+      </c>
+      <c r="Q104" s="11" t="s">
         <v>1785</v>
-      </c>
-      <c r="P104" s="11" t="s">
-        <v>1786</v>
-      </c>
-      <c r="Q104" s="11" t="s">
-        <v>1787</v>
       </c>
       <c r="R104" s="11" t="s">
         <v>24</v>
       </c>
       <c r="S104" s="11" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="T104" s="11" t="s">
         <v>1122</v>
@@ -17574,37 +17568,37 @@
         <v>1008</v>
       </c>
       <c r="W104" s="11" t="s">
-        <v>1788</v>
+        <v>1786</v>
       </c>
       <c r="X104" s="11" t="s">
-        <v>1789</v>
+        <v>1787</v>
       </c>
       <c r="Y104" s="11" t="s">
         <v>1007</v>
       </c>
       <c r="Z104" s="11" t="s">
-        <v>1790</v>
+        <v>1788</v>
       </c>
       <c r="AA104" s="11" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="AB104" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC104" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD104" s="11" t="s">
-        <v>1791</v>
+        <v>1789</v>
       </c>
       <c r="AE104" s="11" t="s">
         <v>996</v>
       </c>
       <c r="AF104" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG104" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH104" s="11" t="s">
         <v>26</v>
@@ -17616,7 +17610,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="105" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>104</v>
       </c>
@@ -17660,34 +17654,34 @@
         <v>994</v>
       </c>
       <c r="O105" s="11" t="s">
-        <v>1792</v>
+        <v>1790</v>
       </c>
       <c r="P105" s="11" t="s">
         <v>1083</v>
       </c>
       <c r="Q105" s="11" t="s">
-        <v>1793</v>
+        <v>1791</v>
       </c>
       <c r="R105" s="11" t="s">
         <v>24</v>
       </c>
       <c r="S105" s="11" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="T105" s="11" t="s">
-        <v>1794</v>
+        <v>1792</v>
       </c>
       <c r="U105" s="11" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="V105" s="11" t="s">
         <v>1008</v>
       </c>
       <c r="W105" s="11" t="s">
-        <v>1796</v>
+        <v>1794</v>
       </c>
       <c r="X105" s="11" t="s">
-        <v>1797</v>
+        <v>1795</v>
       </c>
       <c r="Y105" s="11" t="s">
         <v>1007</v>
@@ -17696,25 +17690,25 @@
         <v>26</v>
       </c>
       <c r="AA105" s="11" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="AB105" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC105" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD105" s="11" t="s">
-        <v>1798</v>
+        <v>1796</v>
       </c>
       <c r="AE105" s="11" t="s">
-        <v>1962</v>
+        <v>1959</v>
       </c>
       <c r="AF105" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG105" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH105" s="11" t="s">
         <v>26</v>
@@ -17726,7 +17720,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="106" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>105</v>
       </c>
@@ -17761,7 +17755,7 @@
         <v>563</v>
       </c>
       <c r="L106" s="4" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="M106" s="4" t="s">
         <v>993</v>
@@ -17770,19 +17764,19 @@
         <v>995</v>
       </c>
       <c r="O106" s="11" t="s">
+        <v>1797</v>
+      </c>
+      <c r="P106" s="11" t="s">
+        <v>1798</v>
+      </c>
+      <c r="Q106" s="11" t="s">
         <v>1799</v>
-      </c>
-      <c r="P106" s="11" t="s">
-        <v>1800</v>
-      </c>
-      <c r="Q106" s="11" t="s">
-        <v>1801</v>
       </c>
       <c r="R106" s="11" t="s">
         <v>24</v>
       </c>
       <c r="S106" s="11" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="T106" s="11" t="s">
         <v>1122</v>
@@ -17794,37 +17788,37 @@
         <v>1008</v>
       </c>
       <c r="W106" s="11" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="X106" s="11" t="s">
-        <v>1803</v>
+        <v>1801</v>
       </c>
       <c r="Y106" s="11" t="s">
         <v>1007</v>
       </c>
       <c r="Z106" s="11" t="s">
-        <v>1804</v>
+        <v>1802</v>
       </c>
       <c r="AA106" s="11" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AB106" s="11" t="s">
         <v>1212</v>
       </c>
       <c r="AC106" s="11" t="s">
+        <v>1803</v>
+      </c>
+      <c r="AD106" s="11" t="s">
+        <v>1804</v>
+      </c>
+      <c r="AE106" s="11" t="s">
         <v>1805</v>
       </c>
-      <c r="AD106" s="11" t="s">
-        <v>1806</v>
-      </c>
-      <c r="AE106" s="11" t="s">
-        <v>1807</v>
-      </c>
       <c r="AF106" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG106" s="11" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH106" s="11" t="s">
         <v>26</v>
@@ -17836,7 +17830,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="107" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>106</v>
       </c>
@@ -17877,19 +17871,19 @@
         <v>1054</v>
       </c>
       <c r="O107" s="32" t="s">
+        <v>1806</v>
+      </c>
+      <c r="P107" s="32" t="s">
+        <v>1807</v>
+      </c>
+      <c r="Q107" s="32" t="s">
         <v>1808</v>
-      </c>
-      <c r="P107" s="32" t="s">
-        <v>1809</v>
-      </c>
-      <c r="Q107" s="32" t="s">
-        <v>1810</v>
       </c>
       <c r="R107" s="13" t="s">
         <v>24</v>
       </c>
       <c r="S107" s="13" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="T107" s="13" t="s">
         <v>1122</v>
@@ -17901,37 +17895,37 @@
         <v>1008</v>
       </c>
       <c r="W107" s="32" t="s">
-        <v>1811</v>
+        <v>1809</v>
       </c>
       <c r="X107" s="32" t="s">
-        <v>1812</v>
+        <v>1810</v>
       </c>
       <c r="Y107" s="32" t="s">
         <v>1007</v>
       </c>
       <c r="Z107" s="32" t="s">
-        <v>1813</v>
+        <v>1811</v>
       </c>
       <c r="AA107" s="32" t="s">
         <v>990</v>
       </c>
       <c r="AB107" s="32" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC107" s="32" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="AD107" s="32" t="s">
         <v>1245</v>
       </c>
       <c r="AE107" s="13" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="AF107" s="13" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG107" s="13" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH107" s="13" t="s">
         <v>26</v>
@@ -17943,7 +17937,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="108" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>107</v>
       </c>
@@ -17987,19 +17981,19 @@
         <v>1054</v>
       </c>
       <c r="O108" s="32" t="s">
+        <v>1812</v>
+      </c>
+      <c r="P108" s="32" t="s">
+        <v>1813</v>
+      </c>
+      <c r="Q108" s="44" t="s">
         <v>1814</v>
-      </c>
-      <c r="P108" s="32" t="s">
-        <v>1815</v>
-      </c>
-      <c r="Q108" s="44" t="s">
-        <v>1816</v>
       </c>
       <c r="R108" s="13" t="s">
         <v>24</v>
       </c>
       <c r="S108" s="13" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="T108" s="13" t="s">
         <v>1122</v>
@@ -18011,37 +18005,37 @@
         <v>1008</v>
       </c>
       <c r="W108" s="32" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="X108" s="32" t="s">
-        <v>1818</v>
+        <v>1816</v>
       </c>
       <c r="Y108" s="32" t="s">
         <v>1007</v>
       </c>
       <c r="Z108" s="32" t="s">
-        <v>1819</v>
+        <v>1817</v>
       </c>
       <c r="AA108" s="32" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AB108" s="32" t="s">
         <v>62</v>
       </c>
       <c r="AC108" s="32" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="AD108" s="32" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="AE108" s="32" t="s">
-        <v>1960</v>
+        <v>1957</v>
       </c>
       <c r="AF108" s="13" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG108" s="32" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH108" s="13" t="s">
         <v>26</v>
@@ -18053,7 +18047,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="109" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>108</v>
       </c>
@@ -18094,13 +18088,13 @@
         <v>1054</v>
       </c>
       <c r="O109" s="2" t="s">
+        <v>1290</v>
+      </c>
+      <c r="P109" s="2" t="s">
         <v>1291</v>
       </c>
-      <c r="P109" s="2" t="s">
+      <c r="Q109" s="42" t="s">
         <v>1292</v>
-      </c>
-      <c r="Q109" s="42" t="s">
-        <v>1293</v>
       </c>
       <c r="R109" s="2" t="s">
         <v>24</v>
@@ -18115,28 +18109,28 @@
         <v>1008</v>
       </c>
       <c r="Z109" s="2" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="AA109" s="2" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AB109" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC109" s="2" t="s">
-        <v>1888</v>
+        <v>1885</v>
       </c>
       <c r="AD109" s="2" t="s">
         <v>1047</v>
       </c>
       <c r="AE109" s="2" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="AF109" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG109" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH109" s="2" t="s">
         <v>26</v>
@@ -18148,7 +18142,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="110" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>109</v>
       </c>
@@ -18189,13 +18183,13 @@
         <v>994</v>
       </c>
       <c r="O110" s="2" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="P110" s="2" t="s">
         <v>1007</v>
       </c>
       <c r="Q110" s="42" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="R110" s="2" t="s">
         <v>24</v>
@@ -18210,28 +18204,28 @@
         <v>1008</v>
       </c>
       <c r="Z110" s="2" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="AA110" s="2" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="AB110" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC110" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD110" s="2" t="s">
         <v>1047</v>
       </c>
       <c r="AE110" s="2" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="AF110" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG110" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH110" s="2" t="s">
         <v>26</v>
@@ -18243,7 +18237,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="111" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>110</v>
       </c>
@@ -18287,13 +18281,13 @@
         <v>1054</v>
       </c>
       <c r="O111" s="2" t="s">
+        <v>1330</v>
+      </c>
+      <c r="P111" s="2" t="s">
         <v>1331</v>
       </c>
-      <c r="P111" s="2" t="s">
+      <c r="Q111" s="42" t="s">
         <v>1332</v>
-      </c>
-      <c r="Q111" s="42" t="s">
-        <v>1333</v>
       </c>
       <c r="R111" s="2" t="s">
         <v>24</v>
@@ -18308,40 +18302,40 @@
         <v>1008</v>
       </c>
       <c r="Z111" s="2" t="s">
+        <v>1335</v>
+      </c>
+      <c r="AA111" s="2" t="s">
+        <v>1842</v>
+      </c>
+      <c r="AB111" s="2" t="s">
+        <v>1333</v>
+      </c>
+      <c r="AC111" s="2" t="s">
+        <v>1896</v>
+      </c>
+      <c r="AD111" s="2" t="s">
         <v>1336</v>
-      </c>
-      <c r="AA111" s="2" t="s">
-        <v>1844</v>
-      </c>
-      <c r="AB111" s="2" t="s">
-        <v>1334</v>
-      </c>
-      <c r="AC111" s="2" t="s">
-        <v>1899</v>
-      </c>
-      <c r="AD111" s="2" t="s">
-        <v>1337</v>
       </c>
       <c r="AE111" s="8" t="s">
         <v>997</v>
       </c>
       <c r="AF111" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG111" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH111" s="2" t="s">
         <v>1216</v>
       </c>
       <c r="AI111" s="2" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="AJ111" s="2" t="s">
         <v>1151</v>
       </c>
     </row>
-    <row r="112" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>111</v>
       </c>
@@ -18382,16 +18376,16 @@
         <v>993</v>
       </c>
       <c r="N112" s="18" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="O112" s="33" t="s">
+        <v>1337</v>
+      </c>
+      <c r="P112" s="4" t="s">
         <v>1338</v>
       </c>
-      <c r="P112" s="4" t="s">
+      <c r="Q112" s="33" t="s">
         <v>1339</v>
-      </c>
-      <c r="Q112" s="33" t="s">
-        <v>1340</v>
       </c>
       <c r="R112" s="4" t="s">
         <v>24</v>
@@ -18403,40 +18397,40 @@
         <v>992</v>
       </c>
       <c r="V112" s="4" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AA112" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="AB112" s="18" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="AC112" s="4" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AD112" s="4" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AE112" s="6" t="s">
         <v>1259</v>
       </c>
       <c r="AF112" s="4" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AG112" s="4" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AH112" s="4" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AI112" s="4" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AJ112" s="4" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
     </row>
-    <row r="113" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
         <v>112</v>
       </c>
@@ -18480,13 +18474,13 @@
         <v>1054</v>
       </c>
       <c r="O113" s="4" t="s">
+        <v>1340</v>
+      </c>
+      <c r="P113" s="4" t="s">
         <v>1341</v>
       </c>
-      <c r="P113" s="4" t="s">
+      <c r="Q113" s="10" t="s">
         <v>1342</v>
-      </c>
-      <c r="Q113" s="10" t="s">
-        <v>1343</v>
       </c>
       <c r="R113" s="4" t="s">
         <v>24</v>
@@ -18501,28 +18495,28 @@
         <v>1008</v>
       </c>
       <c r="Z113" s="4" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="AA113" s="4" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AB113" s="4" t="s">
         <v>54</v>
       </c>
       <c r="AC113" s="4" t="s">
-        <v>1893</v>
+        <v>1890</v>
       </c>
       <c r="AD113" s="4" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="AE113" s="6" t="s">
         <v>997</v>
       </c>
       <c r="AF113" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG113" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH113" s="4" t="s">
         <v>1064</v>
@@ -18534,7 +18528,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="114" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>113</v>
       </c>
@@ -18599,13 +18593,13 @@
         <v>1196</v>
       </c>
       <c r="AA114" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="AB114" s="4" t="s">
         <v>1126</v>
       </c>
       <c r="AC114" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD114" s="4" t="s">
         <v>1239</v>
@@ -18614,10 +18608,10 @@
         <v>996</v>
       </c>
       <c r="AF114" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG114" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH114" s="4" t="s">
         <v>26</v>
@@ -18629,7 +18623,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="115" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>114</v>
       </c>
@@ -18697,22 +18691,22 @@
         <v>990</v>
       </c>
       <c r="AB115" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC115" s="4" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="AD115" s="4" t="s">
         <v>1245</v>
       </c>
       <c r="AE115" s="4" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="AF115" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG115" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH115" s="4" t="s">
         <v>26</v>
@@ -18724,7 +18718,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="116" spans="1:36" s="4" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:36" s="4" customFormat="1" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>115</v>
       </c>
@@ -18789,13 +18783,13 @@
         <v>1249</v>
       </c>
       <c r="AA116" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="AB116" s="4" t="s">
         <v>1126</v>
       </c>
       <c r="AC116" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD116" s="4" t="s">
         <v>1250</v>
@@ -18804,10 +18798,10 @@
         <v>996</v>
       </c>
       <c r="AF116" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG116" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH116" s="4" t="s">
         <v>26</v>
@@ -18819,7 +18813,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="117" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>116</v>
       </c>
@@ -18854,13 +18848,13 @@
         <v>647</v>
       </c>
       <c r="L117" s="2" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="M117" s="2" t="s">
         <v>993</v>
       </c>
       <c r="N117" s="16" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="O117" s="2" t="s">
         <v>1253</v>
@@ -18881,28 +18875,28 @@
         <v>992</v>
       </c>
       <c r="V117" s="2" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AA117" s="2" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="AB117" s="2" t="s">
         <v>1254</v>
       </c>
       <c r="AC117" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD117" s="2" t="s">
-        <v>1868</v>
+        <v>1865</v>
       </c>
       <c r="AE117" s="8" t="s">
         <v>996</v>
       </c>
       <c r="AF117" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG117" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH117" s="2" t="s">
         <v>26</v>
@@ -18914,7 +18908,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="118" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>117</v>
       </c>
@@ -18979,13 +18973,13 @@
         <v>26</v>
       </c>
       <c r="AA118" s="2" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AB118" s="2" t="s">
         <v>77</v>
       </c>
       <c r="AC118" s="2" t="s">
-        <v>1924</v>
+        <v>1921</v>
       </c>
       <c r="AD118" s="2" t="s">
         <v>26</v>
@@ -18994,22 +18988,22 @@
         <v>1259</v>
       </c>
       <c r="AF118" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG118" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH118" s="7" t="s">
         <v>1216</v>
       </c>
       <c r="AI118" s="7" t="s">
-        <v>1938</v>
+        <v>1935</v>
       </c>
       <c r="AJ118" s="2" t="s">
         <v>1151</v>
       </c>
     </row>
-    <row r="119" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>118</v>
       </c>
@@ -19044,13 +19038,13 @@
         <v>868</v>
       </c>
       <c r="L119" s="2" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="M119" s="2" t="s">
         <v>1011</v>
       </c>
       <c r="N119" s="16" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="O119" s="2" t="s">
         <v>1224</v>
@@ -19077,13 +19071,13 @@
         <v>26</v>
       </c>
       <c r="AA119" s="2" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="AB119" s="2" t="s">
         <v>54</v>
       </c>
       <c r="AC119" s="2" t="s">
-        <v>1900</v>
+        <v>1897</v>
       </c>
       <c r="AD119" s="2" t="s">
         <v>1220</v>
@@ -19095,7 +19089,7 @@
         <v>25</v>
       </c>
       <c r="AG119" s="2" t="s">
-        <v>1949</v>
+        <v>1946</v>
       </c>
       <c r="AH119" s="2" t="s">
         <v>1216</v>
@@ -19107,7 +19101,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="120" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>119</v>
       </c>
@@ -19172,25 +19166,25 @@
         <v>1225</v>
       </c>
       <c r="AA120" s="2" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="AB120" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC120" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD120" s="2" t="s">
         <v>1130</v>
       </c>
       <c r="AE120" s="2" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="AF120" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG120" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH120" s="2" t="s">
         <v>26</v>
@@ -19202,7 +19196,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="121" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <v>120</v>
       </c>
@@ -19237,7 +19231,7 @@
         <v>882</v>
       </c>
       <c r="L121" s="2" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="M121" s="2" t="s">
         <v>993</v>
@@ -19264,16 +19258,16 @@
         <v>992</v>
       </c>
       <c r="V121" s="2" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AA121" s="2" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="AB121" s="2" t="s">
         <v>1229</v>
       </c>
       <c r="AC121" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD121" s="36" t="s">
         <v>1230</v>
@@ -19282,22 +19276,22 @@
         <v>1028</v>
       </c>
       <c r="AF121" s="2" t="s">
-        <v>1943</v>
+        <v>1940</v>
       </c>
       <c r="AG121" s="36" t="s">
-        <v>1936</v>
+        <v>1933</v>
       </c>
       <c r="AH121" s="2" t="s">
         <v>1216</v>
       </c>
       <c r="AI121" s="2" t="s">
-        <v>1881</v>
+        <v>1878</v>
       </c>
       <c r="AJ121" s="2" t="s">
         <v>1151</v>
       </c>
     </row>
-    <row r="122" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>121</v>
       </c>
@@ -19356,43 +19350,43 @@
         <v>1013</v>
       </c>
       <c r="T122" s="4" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="V122" s="4" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AA122" s="4" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="AB122" s="4" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AC122" s="4" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AD122" s="4" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AE122" s="4" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AF122" s="4" t="s">
         <v>237</v>
       </c>
       <c r="AG122" s="33" t="s">
-        <v>1939</v>
+        <v>1936</v>
       </c>
       <c r="AH122" s="4" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AI122" s="4" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AJ122" s="4" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
     </row>
-    <row r="123" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>122</v>
       </c>
@@ -19454,28 +19448,28 @@
         <v>992</v>
       </c>
       <c r="V123" s="4" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AA123" s="4" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AB123" s="4" t="s">
         <v>62</v>
       </c>
       <c r="AC123" s="4" t="s">
-        <v>1870</v>
+        <v>1867</v>
       </c>
       <c r="AD123" s="4" t="s">
-        <v>1869</v>
+        <v>1866</v>
       </c>
       <c r="AE123" s="4" t="s">
         <v>1081</v>
       </c>
       <c r="AF123" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG123" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH123" s="4" t="s">
         <v>1064</v>
@@ -19487,7 +19481,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="124" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
         <v>123</v>
       </c>
@@ -19522,13 +19516,13 @@
         <v>904</v>
       </c>
       <c r="L124" s="10" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="M124" s="10" t="s">
         <v>993</v>
       </c>
       <c r="N124" s="18" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="O124" s="10" t="s">
         <v>1202</v>
@@ -19543,46 +19537,46 @@
         <v>24</v>
       </c>
       <c r="S124" s="10" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="T124" s="10" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="V124" s="10" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AA124" s="10" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="AB124" s="10" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC124" s="10" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD124" s="10" t="s">
-        <v>1849</v>
+        <v>1847</v>
       </c>
       <c r="AE124" s="10" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="AF124" s="10" t="s">
-        <v>1941</v>
+        <v>1938</v>
       </c>
       <c r="AG124" s="10" t="s">
-        <v>1940</v>
+        <v>1937</v>
       </c>
       <c r="AH124" s="10" t="s">
         <v>1216</v>
       </c>
       <c r="AI124" s="35" t="s">
-        <v>1882</v>
+        <v>1879</v>
       </c>
       <c r="AJ124" s="10" t="s">
         <v>1151</v>
       </c>
     </row>
-    <row r="125" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
         <v>124</v>
       </c>
@@ -19650,25 +19644,25 @@
         <v>26</v>
       </c>
       <c r="AA125" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="AB125" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC125" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD125" s="4" t="s">
         <v>1209</v>
       </c>
       <c r="AE125" s="4" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="AF125" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG125" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH125" s="4" t="s">
         <v>26</v>
@@ -19680,7 +19674,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="126" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <v>125</v>
       </c>
@@ -19715,7 +19709,7 @@
         <v>236</v>
       </c>
       <c r="L126" s="2" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="M126" s="2" t="s">
         <v>993</v>
@@ -19739,22 +19733,22 @@
         <v>1013</v>
       </c>
       <c r="T126" s="2" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="V126" s="2" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AA126" s="2" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="AB126" s="2" t="s">
         <v>1212</v>
       </c>
       <c r="AC126" s="2" t="s">
-        <v>1891</v>
+        <v>1888</v>
       </c>
       <c r="AD126" s="2" t="s">
-        <v>1871</v>
+        <v>1868</v>
       </c>
       <c r="AE126" s="2" t="s">
         <v>996</v>
@@ -19763,7 +19757,7 @@
         <v>25</v>
       </c>
       <c r="AG126" s="2" t="s">
-        <v>1912</v>
+        <v>1909</v>
       </c>
       <c r="AH126" s="2" t="s">
         <v>1064</v>
@@ -19775,7 +19769,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="127" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <v>126</v>
       </c>
@@ -19831,46 +19825,46 @@
         <v>24</v>
       </c>
       <c r="S127" s="2" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="T127" s="2" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="V127" s="2" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AA127" s="2" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="AB127" s="2" t="s">
         <v>1086</v>
       </c>
       <c r="AC127" s="2" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AD127" s="2" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AE127" s="8" t="s">
         <v>997</v>
       </c>
       <c r="AF127" s="2" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AG127" s="2" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AH127" s="2" t="s">
         <v>1216</v>
       </c>
       <c r="AI127" s="2" t="s">
-        <v>1910</v>
+        <v>1907</v>
       </c>
       <c r="AJ127" s="13" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
     </row>
-    <row r="128" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
         <v>127</v>
       </c>
@@ -19911,7 +19905,7 @@
         <v>1011</v>
       </c>
       <c r="N128" s="16" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="O128" s="2" t="s">
         <v>1070</v>
@@ -19938,25 +19932,25 @@
         <v>26</v>
       </c>
       <c r="AA128" s="2" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AB128" s="2" t="s">
         <v>77</v>
       </c>
       <c r="AC128" s="2" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="AD128" s="2" t="s">
         <v>1074</v>
       </c>
       <c r="AE128" s="8" t="s">
-        <v>1964</v>
+        <v>1961</v>
       </c>
       <c r="AF128" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG128" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH128" s="2" t="s">
         <v>26</v>
@@ -19968,7 +19962,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="129" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
         <v>128</v>
       </c>
@@ -20033,25 +20027,25 @@
         <v>1196</v>
       </c>
       <c r="AA129" s="2" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="AB129" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC129" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD129" s="2" t="s">
         <v>1197</v>
       </c>
       <c r="AE129" s="2" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="AF129" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG129" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH129" s="2" t="s">
         <v>26</v>
@@ -20063,7 +20057,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="130" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <v>129</v>
       </c>
@@ -20128,13 +20122,13 @@
         <v>1200</v>
       </c>
       <c r="AA130" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="AB130" s="4" t="s">
         <v>77</v>
       </c>
       <c r="AC130" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD130" s="4" t="s">
         <v>1201</v>
@@ -20143,10 +20137,10 @@
         <v>996</v>
       </c>
       <c r="AF130" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG130" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH130" s="4" t="s">
         <v>26</v>
@@ -20158,7 +20152,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="131" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
         <v>130</v>
       </c>
@@ -20193,7 +20187,7 @@
         <v>236</v>
       </c>
       <c r="L131" s="4" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="M131" s="4" t="s">
         <v>993</v>
@@ -20217,31 +20211,31 @@
         <v>1013</v>
       </c>
       <c r="T131" s="4" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="V131" s="4" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AA131" s="4" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AB131" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC131" s="4" t="s">
-        <v>1925</v>
+        <v>1922</v>
       </c>
       <c r="AD131" s="4" t="s">
-        <v>1872</v>
+        <v>1869</v>
       </c>
       <c r="AE131" s="5" t="s">
         <v>1259</v>
       </c>
       <c r="AF131" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG131" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH131" s="5" t="s">
         <v>1216</v>
@@ -20253,7 +20247,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="132" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
         <v>131</v>
       </c>
@@ -20312,43 +20306,43 @@
         <v>1013</v>
       </c>
       <c r="T132" s="4" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="V132" s="4" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AA132" s="4" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="AB132" s="4" t="s">
         <v>54</v>
       </c>
       <c r="AC132" s="4" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AD132" s="4" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AE132" s="6" t="s">
         <v>997</v>
       </c>
       <c r="AF132" s="4" t="s">
-        <v>1943</v>
+        <v>1940</v>
       </c>
       <c r="AG132" s="4" t="s">
-        <v>1952</v>
+        <v>1949</v>
       </c>
       <c r="AH132" s="4" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AI132" s="4" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AJ132" s="4" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
     </row>
-    <row r="133" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
         <v>132</v>
       </c>
@@ -20389,7 +20383,7 @@
         <v>1011</v>
       </c>
       <c r="N133" s="18" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="O133" s="4" t="s">
         <v>1059</v>
@@ -20416,13 +20410,13 @@
         <v>1063</v>
       </c>
       <c r="AA133" s="4" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AB133" s="4" t="s">
         <v>54</v>
       </c>
       <c r="AC133" s="4" t="s">
-        <v>1916</v>
+        <v>1913</v>
       </c>
       <c r="AD133" s="4" t="s">
         <v>1062</v>
@@ -20431,10 +20425,10 @@
         <v>997</v>
       </c>
       <c r="AF133" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG133" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH133" s="4" t="s">
         <v>1064</v>
@@ -20446,7 +20440,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="134" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
         <v>133</v>
       </c>
@@ -20508,19 +20502,19 @@
         <v>992</v>
       </c>
       <c r="V134" s="2" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AA134" s="2" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="AB134" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC134" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AD134" s="2" t="s">
-        <v>1873</v>
+        <v>1870</v>
       </c>
       <c r="AE134" s="2" t="s">
         <v>997</v>
@@ -20529,7 +20523,7 @@
         <v>25</v>
       </c>
       <c r="AG134" s="2" t="s">
-        <v>1918</v>
+        <v>1915</v>
       </c>
       <c r="AH134" s="2" t="s">
         <v>26</v>
@@ -20541,7 +20535,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="135" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
         <v>134</v>
       </c>
@@ -20603,28 +20597,28 @@
         <v>992</v>
       </c>
       <c r="V135" s="2" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AA135" s="2" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AB135" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AC135" s="2" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="AD135" s="2" t="s">
-        <v>1874</v>
+        <v>1871</v>
       </c>
       <c r="AE135" s="2" t="s">
         <v>1081</v>
       </c>
       <c r="AF135" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AG135" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AH135" s="2" t="s">
         <v>26</v>
